--- a/result/competitors_all50.xlsx
+++ b/result/competitors_all50.xlsx
@@ -1767,22 +1767,22 @@
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observe.AI</t>
+          <t xml:space="preserve">Noota</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">observe.ai</t>
+          <t xml:space="preserve">noota.io</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Sales Agents</t>
+          <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Call Intelligence, Coaching Intelligence</t>
+          <t xml:space="preserve">Call Intelligence, Shared Memory</t>
         </is>
       </c>
       <c r="E20" s="3">
@@ -1790,2797 +1790,2803 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Contact-centre CX leaders ('CX leaders'); enterprise contact centres ('Securely scaling the world’s largest contact centers'); CX operations and IT buyers</t>
+          <t xml:space="preserve">ANALYST SUMMARY: Organisations by type: Enterprise, Service companies, Public sector, Recruitment, SMBs &amp; startups; footer adds Sales teams and Consulting &amp; agencies; European teams</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: SOP changes need engineering help ('so every change is a ticket'); CRM and backend integration is where teams get stuck; manual QA on a small sample of interactions and delayed reporting</t>
+          <t xml:space="preserve">ANALYST SUMMARY: Meeting admin and lost follow-up ('Fewer administrative tasks'); bots in the call; data-sovereignty concerns for European buyers</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purpose-built AI agents. One CX platform.</t>
+          <t xml:space="preserve">The sovereign AI Assistant that follows you everywhere</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">What We Do &amp; How We Transform CX</t>
+          <t xml:space="preserve">From the brief to the follow-up, Noota handles every meeting.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Observe.AI’s Agentic CX Platform uses AI Agents to resolve interactions and improve CX outcomes</t>
+          <t xml:space="preserve">On your desktop, in your inbox and on your phone: Noota remembers every conversation and gets the work done for you.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request demo</t>
+          <t xml:space="preserve">Start for free</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Our platform</t>
+          <t xml:space="preserve">Book a demo</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What We Do &amp; How We Transform CX
-AI-Driven Outcomes We Deliver
-Beyond Expectations</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observe.AI transforms CX with purpose-built AI agents that resolve customer inquiries, empower frontline teams, and optimize operations—on one unified platform for faster, more consistent outcomes.</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'The only CX platform built around purpose‑made AI agents—unifying automation, agent assist, and analytics for faster, more consistent outcomes.' (&lt;p&gt; under the 'Why Choose Observe.AI' H2)</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.observe.ai/</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H1 verified as HTML &lt;h1&gt;; eyebrow "NEW Meet Performance Agents. Now Available." verified as div above H1 (visible text, not heading); H2 = first H2 ("What We Do &amp; How We Transform CX"); hero paragraph verified verbatim; primary CTA "Request demo" verified from HTML anchor (-&gt; /demo); secondary CTA "Our platform" verified from HTML anchor (-&gt; /ai-agents/customers); section headings verified as HTML &lt;h2&gt; in document order; Positioning exact verbatim from homepage paragraph; ICP "CX leaders" from body text "Real results from CX leaders using Observe.AI’s AI agents" (also "the world’s largest contact centers" in div text); Pain Point "Not verified" — no explicit pain-point statement found on homepage (original Master Report pain "SOP-to-agent-logic bottleneck" not stated on homepage). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: Pain Point filled from the homepage &lt;p&gt; under H3 'Faster, Better Resolutions' in the 'AI-Driven Outcomes We Deliver' section (section_outcomes) of https://www.observe.ai/ (the earlier 'no explicit pain-point statement' note is superseded; this sentence matches the Master Report pain 'SOP-to-agent-logic bottleneck'). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; operations page); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: Quote is the &lt;p&gt; directly under the H2 'Why' / 'Choose Observe.AI' (two &lt;h2&gt; elements) in a main section. HTTP 200, no redirect. Homepage researched Oct 19, 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Noota</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">noota.io</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conversation Intelligence</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call Intelligence, Shared Memory</t>
-        </is>
-      </c>
-      <c r="E21" s="3">
-        <v>3</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Organisations by type: Enterprise, Service companies, Public sector, Recruitment, SMBs &amp; startups; footer adds Sales teams and Consulting &amp; agencies; European teams</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Meeting admin and lost follow-up ('Fewer administrative tasks'); bots in the call; data-sovereignty concerns for European buyers</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The sovereign AI Assistant that follows you everywhere</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From the brief to the follow-up, Noota handles every meeting.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On your desktop, in your inbox and on your phone: Noota remembers every conversation and gets the work done for you.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Start for free</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Book a demo</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">From the brief to the follow-up, Noota handles every meeting.
 One assistant, wherever you work
 Record without a bot</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Noota is an AI collaborator that records, transcribes and summarizes your meetings, calls and interviews, then does the follow-up work for you: structured meeting notes, action items assigned to the right people, follow-up emails and updates to your CRM or ATS.</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Unlike a simple AI note taker, Noota works before, during and after each meeting.' (FAQ answer under H3 'What is Noota? An AI note taker and meeting assistant for your whole workday') | 'The sovereign alternative' (&lt;p&gt; below the hero, above the logo strip)</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.noota.io/</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">H1 verified as HTML &lt;h1&gt;; H2 = first H2 ("From the brief to the follow-up, Noota handles every meeting." — also Section Heading 1); hero paragraph verified verbatim; primary CTA "Start for free" verified from HTML anchor (-&gt; app.noota.io/register); secondary CTA "Book a demo" verified from HTML anchor (-&gt; /book-a-demo); G2/Trustpilot badge links (4.9 on G2 (314), 4.9 on Trustpilot (104)) verified as badge links in hero, not counted as CTAs; hero trust signals ("Data hosted in Europe", "No bot joins your call", "GDPR compliant, ISO 27001 practices") verified as badge paragraphs; section headings verified as HTML &lt;h2&gt; in document order (Section 3 "Record without a bot" is the first heading of a feature section containing sub-headings "Your inbox is Noota’s memory", "Ask anything about any conversation", "Every commitment tracked and done"); Positioning exact verbatim from FAQ paragraph (full 262-character statement, ending "updates to your CRM or ATS."); ICP "Not verified" — "Agencies, search firms, in-house teams" was found to be a nav-dropdown item description (nav-item_desc inside navbar_dropdown, describing the "Recruitment" menu link), not a general ICP statement; "thousands of other teams across Europe" appears in testimonial section but is not a stated ICP; Pain Point "Not verified" — no explicit pain-point statement found on homepage. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (ICP: the homepage names organisation types only in the nav 'By organisation' dropdown and footer 'Solutions' links, and the Sales Agent page https://www.noota.io/features/sales-agent addresses reps and managers of a 'coming soon' add-on, not a site-wide ICP; Pain Point: no explicit pain-point statement on either page). Wording drift noted: today's capture shows feature H2s 'Your inbox, sorted and answered', 'Ask anything, get a sourced answer' and 'Every commitment becomes a task', not the sub-headings listed above; H1, H2, hero copy, CTAs and Section Headings 1-3 are unchanged. ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; Sales Agent page (coming soon)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1 opens the second paragraph of the FAQ answer under H3 'What is Noota? An AI note taker and meeting assistant for your whole workday' (FAQ section after 'Still have a question?'). Quote 2 is a &lt;p&gt; directly after the hero trust points ('Data hosted in Europe', 'No bot joins your call'). HTTP 200, no redirect. Homepage researched Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Zoom (Revenue Accelerator)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">zoom.com</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E22" s="3">
+      <c r="E21" s="3">
         <v>6</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Sales teams ('modern sales teams'); persona cards target Revenue leaders, Sales managers, Sales reps; CRO page for revenue leaders</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Tool sprawl ('without juggling a dozen different tools'); sellers miss what matters in conversations; leaders lack forecast clarity and chase reps for deal status</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation intelligence software that accelerates revenue</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Why Zoom Revenue Accelerator?</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Identify high-potential contacts that are more likely to convert. Nail the live conversation. Get better at both, every day. Zoom Revenue Accelerator connects insight to action across your revenue cycle.</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Contact sales</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Why Zoom Revenue Accelerator?
 Complete conversation intelligence software for modern sales teams
 Discover how teams use Zoom Revenue Accelerator</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Zoom Revenue Accelerator connects insight to action across your revenue cycle.</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Zoom Revenue Accelerator stands out in the competitive landscape by offering a complete AI-driven platform that helps your sales team perform better at every stage of the revenue journey.' (FAQ answer to 'What differentiates Zoom Revenue Accelerator from other conversation intelligence software?') | 'Cost-effective: Delivers enterprise-level capabilities without the enterprise price tag, making powerful conversation intelligence accessible for teams of all sizes.' (same FAQ answer, 'five key differentiators' list)</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.zoom.com/en/products/conversation-intelligence/</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Entity note: Master Report entry is "Zoom (Revenue Accelerator)" — suite vendor; the Revenue Accelerator product landing page (zoom.com/en/products/conversation-intelligence/) was captured, not the zoom.com corporate homepage (HTTP 200, no redirect). H1 verified as HTML &lt;h1&gt; (h1.hero__title inside section.hero); H2 = first body H2 ("Why Zoom Revenue Accelerator?"); global nav/mega-menu and footer headings excluded. Hero paragraph verified verbatim from div.hero__body-text. Primary CTA "Contact sales" verified as HTML anchor in div.hero__cta (-&gt; /en/products/conversation-intelligence/#form, an on-page contact form; anchor also carries a visually-hidden duplicate span "Contact sales", not counted twice); secondary CTA "Not verified" — hero__cta contains only one anchor. Section headings verified as HTML &lt;h2&gt; in document order; H3 feature cards ("Create more qualified pipeline" etc.), swiper persona-card H3s ("Revenue leaders", "Sales managers", ...) and feature-accordion tab buttons excluded as card/tab content. Positioning = final sentence of the hero paragraph. ICP "modern sales teams" from exact H2 "Complete conversation intelligence software for modern sales teams"; Master Report's "Small team to large enterprise" phrase was NOT found in the captured HTML. Pain Point exact verbatim from FAQ answer "What differentiates Zoom Revenue Accelerator from other conversation intelligence software?" (accordion content in main, present in HTML). Related messaging relevant to PitchSense: persona card "call libraries support new hire training and sharing best practices"; accordion "Automatically update your CRM with deal outcomes so teams can learn from every closed opportunity"; "ZRA Forecast gives rep-to-CRO visibility" (vendor claims). Customer-story metrics (e.g. Barracuda "close 15% more deals") are vendor claims, recorded not endorsed. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: div.hero__cta in the homepage capture holds only the one 'Contact sales' anchor; no second hero CTA exists in the HTML). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; CRO page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: first sentence of the &lt;p&gt; answer under the FAQ accordion &lt;button&gt; 'What differentiates Zoom Revenue Accelerator from other conversation intelligence software?' (section.accordion). Quote 2: fifth &lt;li&gt; of the 'five key differentiators' list in the same answer. Both present in server HTML (accordion content, not client-side only). Capture: phase2/batches/batch06/captures/zoom_home.html (Revenue Accelerator product page per entity resolution). Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Traq.ai</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">traq.ai</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E23" s="3">
+      <c r="E22" s="3">
         <v>6</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Sales and RevOps leaders ('VPs of Sales and Directors of Revenue Operations'), named below the hero; later sections address sales managers and salespeople</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Forecasts and CRM rest on typed-in data, not what was said ('Your forecast is fiction.'); four blind spots: uneven coaching, deal blind spots, admin hours, deals that go quiet</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence, Reinvented</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your forecast is fiction.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TRAQ turns every customer conversation into structured data. One clean AI layer feeding your CRM, your forecasts, your coaching. What actually happened. What your top performers do right. Codified. Repeatable.</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a Live Demo</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start a Free Trial</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Four blind spots costing you revenue, and how TRAQ closes each one.
 Build a scalable, personalized coaching system with TRAQ.
 Why revenue teams are switching from legacy conversation intelligence platforms</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One clean AI layer feeding your CRM, your forecasts, your coaching.</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Why revenue teams are switching from legacy conversation intelligence platforms' (comparison section H2, eyebrow 'traq vs. the alternatives') | 'Legacy conversation intelligence tools were built for enterprise procurement cycles, not fast-moving sales orgs. TRAQ was built to get you live in days, coach every rep automatically, and prove ROI from month one.' (comparison section intro paragraph)</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.traq.ai/</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Homepage fetched HTTP 200, no redirect (WordPress/Divi). H1 verified as HTML &lt;h1&gt;; H2 = first H2, a Divi dual-heading in the hero whose text is split across three spans ("Your forecast is " + "fiction" + ".") — joined verbatim; a second hero H2 "Your CRM only knows what got typed in." follows immediately (also hero). Hero paragraph verified verbatim as &lt;p&gt;; a further hero div reads "Most “at risk” deals were never marked at risk in the CRM. TRAQ listens to what was actually said, not what got typed into a pipeline stage after the fact." CTAs verified from HTML anchors in the hero button module: "Book a Live Demo" (-&gt; calendly.com/traq/20-minute-traq-ai-demo?month=2026-08) and "Start a Free Trial" (-&gt; traq.ai/pricing/#plans). Section headings = first three post-hero body H2s in document order (the two hero H2s excluded as hero content); footer H2s ("Sales Solutions", "Company", etc.) excluded. Positioning = exact sentence from hero paragraph. ICP exact from body paragraph "For VPs of Sales and Directors of Revenue Operations, the hardest part of scaling a team isn’t finding more pipeline."; homepage stat "350+" / "sales organizations rely on TRAQ" (vendor claim). Pain Point exact first sentence of the hero div quoted above (curly quotes preserved) — directly relevant to PitchSense CRM-truth / shared-memory themes. ROI figures ("28% increase in win rate", "33% faster" ramp, "5 to 7 hours per rep, per week") are vendor claims, recorded not endorsed. Pricing H2 "Starting at $39 per user" present on page. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row has no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; CRO page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: HTML &lt;h2&gt; under the &lt;p&gt; eyebrow 'traq vs. the alternatives'. Quote 2: the &lt;p&gt; directly below it, introducing a 'Capability / Other Platforms / TRAQ' &lt;table&gt; (rows: time to go live, pricing model, coaching depth, mobile &amp; in-person capture, AI follow-up, contract terms). Excluded: nav 'Why TRAQ?' and footer 'TRAQ vs. Granola' links. Capture: phase2/batches/batch06/captures/traq_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HubSpot (Breeze)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">hubspot.com</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Content Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E24" s="3">
+      <c r="E23" s="3">
         <v>3</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Sales reps and their leaders ('sales reps'); hero says 'your whole team'; customer quotes from heads of lead gen and directors of sales</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Reps cannot tell which accounts are ready and spend time researching ('Most reps have no way to know which accounts are actually ready.'); uneven rep performance ('Make every sales rep your best rep.')</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Make every sales rep your best rep.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">More leads. More meetings. More wins.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Prospecting agent researches accounts, finds the right contacts, and drafts personalized outreach, so your whole team prospects like your top sales performer.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get a demo</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">More leads. More meetings. More wins.
 From signal to send.
 See prospecting agent in action.</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HubSpot's AI-powered prospecting agent is a sales automation tool built into HubSpot Sales Hub.</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.hubspot.com/products/sales/ai-prospecting-agent</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Entity note: Master Report entry is "HubSpot (Breeze)" — suite vendor; the Breeze Prospecting Agent product landing page was captured (the page used as evidence in the Master Report), not the hubspot.com corporate homepage; breadcrumb on page: Home &gt; Agent Hub &gt; Prospecting Agent (HTTP 200, no redirect). H1 verified as HTML &lt;h1&gt;; eyebrow "PROSPECTING AGENT" verified as &lt;p&gt; tagline (not a heading). H2 = first body H2; global-nav mega-menu H2/H3s ("The HubSpot Customer Platform", hub cards) and footer H2s excluded. Hero paragraph verified verbatim (p.wf-page-header__description). Primary CTA verified as HTML anchor (-&gt; offers.hubspot.com/sales-demo); visible text "Get a demo" plus visually-hidden span "of Breeze" (screen-reader only, excluded from the recorded text); secondary CTA "Not verified" — hero CTA wrapper contains only one anchor. Section headings verified as HTML &lt;h2&gt; in document order; "From signal to send." appears twice (responsive desktop/accordion duplicate) — counted once; stat H3s (76%/80%/26%, vendor claims) excluded as card content. Positioning exact from FAQ answer "What is HubSpot's AI-powered prospecting agent?". ICP "sales reps" exact from the same FAQ answer ("...so sales reps spend less time researching and more time closing deals"). Pain Point exact from accordion text under "Reach out to leads at exactly the right moment." Shared-memory relevant text: "The more your team uses it, the better the outreach gets" (Master Report quoted "the better it gets" — that wording was NOT found in the captured HTML); "Data agent" card: "Get instant customer insights from your CRM, calls, and documents."; "Breeze Assistant": "Get answers grounded in your CRM data and role". Pricing "$1/per lead" on page. "TRUSTED BY 306,000 CUSTOMERS WORLDWIDE" is a vendor claim. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: the hero CTA wrapper in the homepage capture holds only the one 'Get a demo' anchor; no second hero CTA exists in the HTML). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; Sales Hub CRO page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: No comparison, 'only/first/#1', 'why' or competitive-displacement claim in the body of the Breeze Prospecting Agent product page (H1, H2s, H3s, FAQ accordion checked). Considered and excluded: pricing-card line 'Prospecting agent is built into HubSpot's Smart CRM — that's why you only pay when it delivers results.' (pricing model, no comparison to alternatives); 'Why HubSpot?' / 'Why Choose HubSpot?' and 'Software Comparisons Library' appear only in global nav and footer (excluded). Capture: phase2/batches/batch06/captures/hubspot_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hyperbound</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">hyperbound.ai</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E25" s="3">
+      <c r="E24" s="3">
         <v>6</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Revenue teams ('revenue teams'); hero addresses 'every rep'; customer stories voiced by a CRO, sales strategy and enablement leaders</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: No explicit problem statement; implied uneven rep execution against the buyer ('Help every rep read the buyer and act like your best.'); CRO page adds deal risk and slipping execution</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Know your buyers. Guide every seller.</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How it works</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Help every rep read the buyer and act like your best. Practice with realistic AI buyers, uncover what works in real calls, and get guidance during conversations and across deals.</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a demo</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Try a roleplay</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How it works
 Better selling shows up in the results.
 Bring better selling to every team, market, and language.</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Hyperbound is an AI sales coach that intelligently analyzes your sales calls and helps your reps practice the scenarios they struggle with the most.</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.hyperbound.ai/</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Homepage fetched HTTP 200, no redirect. H1 verified as HTML &lt;h1&gt; (contains &lt;br&gt; between "Know your buyers." and "Guide every seller." — rendered with a single space); H2 = first body H2 ("How it works"). Hero paragraph verified verbatim (p.home-hero-description; source line-wrap whitespace normalized). CTAs verified from HTML anchors in div.home-hero-aside: "Book a demo" (-&gt; /book-a-demo) and "Try a roleplay" (-&gt; app.hyperbound.ai/buyers?invite=hyperbound-website); both repeated in closing section. Section headings verified as HTML &lt;h2&gt; in document order (H2 &lt;br&gt; line breaks rendered as spaces); product-tab H3s ("Practice what wins.", "Make the right move in real calls.", "Turn insight into action.") excluded as tab content of "How it works". Positioning exact from FAQ answer ("How does Hyperbound work alongside our LMS?") — the Master Report's "AI-Powered Roleplay Platform" phrase was NOT found in the captured HTML (homepage messaging has shifted to Practice / Perform / Kota Activate). ICP "revenue teams" exact from trust-strip paragraph "Helping revenue teams put their best selling to work." Pain Point "Not verified" — no explicit pain statement on homepage ("We’re adding fifteen reps next quarter. We can’t keep relying on shadowing alone." is mock UI conversation content, not a vendor pain statement). Shared-memory relevant: "Calls, roleplays, email, CRM, and Slack — connected through your buyers, deals, and reps." verified in HTML but inside p.home-visually-hidden (screen-reader text for a graph graphic); "Kota Activate": "Connect calls, deals, and practice to deliver coaching and next steps where your reps work."; new private-preview links "Agentic Enablement", "Live Call Coaching", "Deal Strategist". Customer quotes (Vanta CRO etc.) are vendor-selected testimonials. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Pain Point: no explicit vendor pain statement in the homepage body or on the CRO page /product/kota-activate; the only pain-like line, 'We’re adding fifteen reps next quarter. We can’t keep relying on shadowing alone.', is mock product-UI dialogue, and Kota copy such as 'so nothing ever slips' is benefit copy, not a pain statement). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; CRO page (Kota)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: No comparison, 'only/first/#1', 'why Hyperbound' or displacement claim in the homepage body (hero, How it works, Customer stories, Built for enterprise, Integrations, FAQ checked). Not differentiation claims: '4.9 Rated on G2' (trust bar) and the banner 'Hyperbound is named in Gartner's Market Overview for B2B Sales AI Roleplay Applications.' (analyst mention, vendor claim). Excluded: nav 'Comparisons — See how Hyperbound stacks up against other tools.' linking to /blog/category/comparisons (not fetched). Capture: phase2/batches/batch06/captures/hyperbound_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Aviso</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">aviso.com</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence &amp; RevOps</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E26" s="3">
+      <c r="E25" s="3">
         <v>4</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: GTM teams ('Modern GTM Teams'), from BDRs to CROs; CRO page and TCO section target CROs and VPs of Sales; RevOps</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Point-tool sprawl and CRM burden ('lower CRM burden and cost'); forecasts built on incomplete data ('Avoid being misguided by incomplete CRM data'); rep time lost</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Build Tomorrow's AI Workforce Today with Aviso</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get back up to 20 hours per rep weekly with Agentic AI</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Agentic AI Platform for Modern GTM Teams to Predict, Guide, and Simplify Every Revenue Action</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book A Demo</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Talk to Ava</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get back up to 20 hours per rep weekly with Agentic AI
 Consolidate Your Tech Stack &amp; Maximize ROI with One Agentic AI Platform
 People love using Aviso</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One Agentic AI Platform for Modern GTM Teams to Predict, Guide, and Simplify Every Revenue Action</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'I harnessed my learnings of 25 years to build the ultimate revenue intelligence platform at Aviso' (CEO quote under H2 'Why Aviso is Different') | 'There is no other platform on the market with such rich functionality. The competition tends to be point solutions that add up to a higher TCO and require separate integrations, eating up the time of your IT team.' (customer testimonial, testimonials carousel)</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.aviso.com/</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Homepage fetched HTTP 200, no redirect (Framer site). H1 ROTATES: the hero is built from multiple HTML &lt;h1&gt; elements — "Build Tomorrow's" + a rotating word element ("AI Workforce", "Agentic Workflows", "Agent Stack" in HTML order) + "Today with Aviso"; each static part appears 3x as responsive (ssr-variant) duplicates. Recorded H1 uses the first rotating value seen in HTML; other values noted here. H2 = first body H2. Hero paragraph verified verbatim as &lt;p&gt;; "Trusted by 450+ Revenue Teams" also in hero (vendor claim). CTAs: "Book A Demo" and "Talk to Ava" verified as HTML &lt;a&gt; elements inside div#hero but the hero anchors carry NO href in the server-rendered HTML (destinations set client-side; not confirmed); a nav "Book A Demo" anchor points to ./book-a-demo. Section headings verified as HTML &lt;h2&gt; in document order; Section 2 contains &lt;br&gt; line breaks (rendered as spaces); "Powered by" H2 excluded — verified as a stat-block label inside the same section as "Consolidate Your Tech Stack..." (not an independent section); responsive duplicates ("People love using Aviso" x3, "Guidance For Every Revenue Activity" x2, etc.) counted once; nav/menu/footer headings excluded. Positioning = hero paragraph (no separate positioning statement). ICP "Modern GTM Teams" exact from hero; body also says "13-week cadences for BDRs to CROs". Pain Point exact phrase from body paragraph "Aviso’s AI-powered mobile app combines predictive forecasting, pipeline management, deal guidance, conversational intelligence, and other capabilities to help revenue teams close more revenue and lower CRM burden and cost." Other pain-type copy: "kill single-threading"; "Move away from mismatched prospects, spammy outreach, and a prospecting-only mindset." Claims ("Get back up to 20 hours per rep weekly", "40%" win-rate increase, "70%+", "Be nearly 100% accurate", "$100m to $1b") are vendor claims, recorded not endorsed. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row has no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; CRO page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: &lt;p&gt; CEO quote (Trevor A. Rodrigues-Templar, &lt;h3&gt;) directly under HTML &lt;h2&gt; 'Why Aviso is Different'. Quote 2: customer testimonial &lt;p&gt; in the testimonials section under &lt;h2&gt; 'What industry leaders have to say about Aviso' (appears twice: carousel duplicate); a customer quote hosted by the vendor, recorded not endorsed. Also on page: top banner 'Aviso named a Leader and a Customer Favorite in The Forrester Wave™ Q3 2026.' Excluded: 'Aviso vs Clari/BoostUp/Gong/People AI/Salesloft/Outreach/Drift/Glean' links in footer. Framer site; quotes present in server HTML. Capture: phase2/batches/batch06/captures/aviso_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Siro</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">siro.ai</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence (field sales)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E27" s="3">
+      <c r="E26" s="3">
         <v>5</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: In-person sellers ('in-person sellers'): field, store and B2B sales teams; persona cards for Sellers, Sales managers, Owners &amp; executives; home-services sales leaders</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Guesswork ('Most sales teams today still run on guesswork.'): in-person conversations go uncaptured, ride-alongs sample a few, playbooks are generic, CRM notes are 'three lines typed from memory'</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI for in-person sellers.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A win for every seat on your team.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Record every customer conversation and use AI to run, evaluate, and improve your business.</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a demo</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">See how it works</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A win for every seat on your team.
 Most sales teams today still run on guesswork.
 Science for the art of sales.</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Siro is an end-to-end sales performance system.</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Most AI sales coaching tools were built for video calls and inside sales teams. Siro handles those too, but was optimized for sellers on-the-go.' (FAQ answer to 'How is Siro different from AI sales coaching tools?') | 'There are other products built for in-person conversations. Siro is the platform built for adoption and focused on results.' (same FAQ answer)</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.siro.ai/</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched 200, no redirect. H1 verified as the only HTML &lt;h1&gt; (inner &lt;span class="whitespace-nowrap"&gt;in-person&lt;/span&gt; flattened); H2 = first body H2 ("A win for every seat on your team."); hero paragraph verified verbatim as the &lt;p&gt; directly after the H1 in the hero section; CTAs verified from hero anchors: "Book a demo" -&gt; /demo, "See how it works" -&gt; /how-it-works (header-nav duplicates excluded); section headings verified as HTML &lt;h2&gt; in document order — Section Heading 3 is split across two &lt;button&gt; elements inside one &lt;h2&gt; ("Science for" / "the art of sales.", an interactive science/art toggle rendered on two lines), recorded with a single joining space; card H3s (Sellers / Sales managers / Owners &amp; executives) and the three-times-repeated metric-carousel H3s ("17%Increase in Units Sold" etc.) excluded as card/carousel duplicates; Positioning exact sentence from the FAQ answer to "01What is Siro?" (accordion panel present in server HTML; full answer continues "Sellers record conversations on their device, and Siro uses what was said to handle notes, follow-ups and CRM updates, score each conversation against your process, and coa[ch]..."); ICP "in-person sellers" from exact H1 text; Pain Point exact H2, supported by body paragraph "The conversations that decide a sale contain some of the most valuable data a business has. Today, most of it isn't captured. What's left for sales teams often relies on guessing." Vendor claims recorded not endorsed: "+17% more units sold, on average, by Culligan dealers using Siro", "Trusted by thousands of sales teams", SOC 2 Type II/HIPAA/GDPR. Notable: homepage advertises "Two-way CRM sync, a REST API, webhooks, and an MCP server making your data agent-friendly" and an "In their office" B2B segment ("keeps each account’s history in one place") beyond field sales. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row has no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; evaluate page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Both quotes are &lt;p&gt; elements in the answer under the FAQ question &lt;span&gt; 'How is Siro different from AI sales coaching tools?' (section.scroll-mt-28), present in server HTML. Capture: phase2/batches/batch07/captures/siro_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Microsoft (Copilot for Sales)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adoption.microsoft.com/copilot-for-sales</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E28" s="3">
+      <c r="E27" s="3">
         <v>4</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Sellers ('Designed for sellers') in organisations adopting Copilot; adoption-page role tabs for Leadership, User enablement, Technical readiness</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Not stated on the inspected pages; leads with Copilot for Sales adoption (hero: 'help sellers save time, focus on customers, and close more deals')</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sales solution in Microsoft Copilot</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Find the right tools</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Designed for sellers, sales solution in Microsoft Copilot brings sales data and insights in the flow of work to help sellers save time, focus on customers, and close more deals. Sales solution in Microsoft Copilot is experienced within Microsoft 365 and connects directly to Dynamics and Salesforce CRMs for real-time data and updates.</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Find the right tools
 Choose your role
 Other Copilot experiences</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Designed for sellers, sales solution in Microsoft Copilot brings sales data and insights in the flow of work to help sellers save time, focus on customers, and close more deals.</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://adoption.microsoft.com/en-us/copilot-for-sales/</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Entity note: product landing page used per entity resolution. Marketing page https://www.microsoft.com/en-us/microsoft-365/copilot/copilot-for-sales returned HTTP 200 but served a bot-block page (&lt;title&gt; "Your request has been blocked..."; H2 "Your current User-Agent string appears to be from an automated process") with two different browser User-Agents; WebFetch timed out (60s) — recorded as unfetchable, consistent with Phase 1. Other guessed microsoft.com Copilot-for-Sales URLs returned 404. Fallback = official Microsoft Adoption product page (the page cited in Master Report Table A), https://adoption.microsoft.com/copilot-for-sales/ -&gt; redirected to /en-us/copilot-for-sales/; &lt;title&gt; "Microsoft Copilot for Sales – Microsoft Adoption". This is an adoption/enablement page, not a demand-gen marketing page. Rebrand: the page's H1 and copy now call the product "Sales solution in Microsoft Copilot" (title still says Copilot for Sales). H1 verified as the only HTML &lt;h1&gt;; hero paragraph verified verbatim (p.no-margin in page-header); Primary/Secondary CTA "Not verified" — page-header contains no CTA anchor or button; the top-bar "Register now" link (ESPC conference promo -&gt; aka.ms/scale/ipm/27001b) excluded as a site-wide event banner; first body links are resource cards ("View the kit" -&gt; /copilot-for-sales/success-kit, "Learn more" -&gt; docs, "Join now" -&gt; community forum). H2/section headings verified as HTML &lt;h2&gt; in document order; tab-panel H3s (Get ready / Onboard &amp; engage / Deliver impact / Extend &amp; optimize, repeated per role tab Leadership / User enablement / Technical readiness) excluded as tab content; product-card H3s excluded. Positioning = first sentence of the hero paragraph; ICP "sellers" from exact phrase "Designed for sellers"; Pain Point "Not verified" — no explicit pain statement on the page. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Primary/Secondary CTA: page-header still contains no CTA anchor or button; Pain Point: no explicit pain statement on the page; no CRO page available: the linked /sales-solution/ page returns 'Page not found' and the microsoft.com marketing page is bot-blocked). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; adoption page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: The analysed page is the Microsoft Adoption product page (marketing page served a bot-block, see row Verification). Its body is enablement content (H1 'Sales solution in Microsoft Copilot'; H2s 'Find the right tools', 'Choose your role', 'Other Copilot experiences', etc.); no comparison, 'only/first/#1', 'why' or displacement claim found. Capture: phase2/batches/batch07/captures/microsoft_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Salesforce (Agentforce)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">salesforce.com/agentforce</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">None documented</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">0 (+1 unverified)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Service-led homepage: role cards for Customer Service, Contact Center, Field Service, Employee Service, Sales Service, IT Service; Sales page addresses sellers</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Rigid chatbots and hold times ('Lose the rigid chatbots and hold times.'); Sales page: seller admin ('Agents handle the grind.') and lost context ('Revenue breaks where context goes.')</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Agentforce</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Five new ways to put agents to work</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Agentforce is the AI agent platform that delivers 24/7 autonomous support at enterprise scale. Lose the rigid chatbots and hold times. Extend agents anywhere customers are: On the web, on the phone, or in apps. Let humans do what they do best, and let Agentforce do the rest.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Access all demos</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Five new ways to put agents to work
 Over 18K companies already run on Agentforce. Join them.
 Better outcomes for everyone. That's the point.</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Agentforce is the AI agent platform that delivers 24/7 autonomous support at enterprise scale.</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'The #1 Leader by G2 for:' (G2 promotion section heading, followed by list 'AI Agents', 'AI Customer Support Agents', 'AI Agent Builders', 'Conversational Interface Agents') | 'Lose the rigid chatbots and hold times.' (hero paragraph)</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.salesforce.com/agentforce/</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Entity note: Agentforce product landing page used per entity resolution (not salesforce.com corporate homepage). https://www.salesforce.com/agentforce/ redirected to /agentforce/?bc=OTH (tracking parameter only). H1 verified as the only HTML &lt;h1&gt; — it is the eyebrow label (h1.eyebrow__label) with text "Agentforce"; the large visible headline is a div.marquee__headline--standard containing only "with Agentforce" in the server HTML (no prefix text present; likely completed client-side — not confirmed, so not recorded as H1/H2); hero bullets "Drive outcomes" / "Scale service" / "Resolve cases" not included. H2 = first body H2. Hero paragraph verified verbatim from div.blade__description. Primary CTA "Access all demos" verified as hero anchor (aria-label "Access all demos: with Agentforce") -&gt; /agentforce/demos/overview/?d=pbv0; Secondary CTA "Not verified" — hero contains only one CTA; the top notification bar link "See more details &amp; register here" (Agentforce Coworker Webinar, October 20th -&gt; invite.salesforce.com/coworker1) excluded as a promo banner. Section headings verified as HTML &lt;h2&gt; in document order; the six role-card H3s preceding the first H2 (Customer Service, Contact Center, Field Service, Employee Service, Sales Service, IT Service) excluded as cards. Positioning = first sentence of hero paragraph; ICP "Not verified" — no explicit target-customer statement ("Over 18K companies already run on Agentforce" is a scale claim, "enterprise scale" describes delivery not buyer); Pain Point exact sentence from hero paragraph. Note: hero messaging is service-led ("24/7 autonomous support"); sales appears as card "Sales Development" ("handling objections, and booking meetings for sales reps"). Memory-relevant copy verified verbatim: "Let agents pursue goals across days and weeks, retain context, adapt their plans, and complete multi-touch workflows with human oversight." and "Route work, share context, and coordinate specialized agents...". Vendor claim recorded not endorsed: "Gartner named Salesforce a Leader in the 2026 Magic Quadrant™ for Conversational AI Platforms — grounded in Data 360 and Customer 360, so every agent knows the customer before it says a word." Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: hero contains a single CTA anchor; ICP: no explicit target-customer statement on the Agentforce page; the CRO page https://www.salesforce.com/sales/ describes Sales Cloud buyers ('sales teams of every size and every industry'), a different product page, so it was not used for the Agentforce ICP). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; Sales page /sales/); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: &lt;div&gt; heading in promotion section (section#1739303865247_vx8_6169814) followed by &lt;li&gt; items 'AI Agents', 'AI Customer Support Agents', 'AI Agent Builders', 'Conversational Interface Agents' and a 'Read the reviews' link (vendor-cited G2 ranking). Quote 2: sentence in the hero &lt;p&gt; (section#agentforce-command-hero) under H1 'Agentforce' (competitive-displacement line vs chatbots). Also on page: 'Gartner named Salesforce a Leader in the 2026 Magic Quadrant™ for Conversational AI Platforms' (promo section). Capture: phase2/batches/batch07/captures/salesforce_home.html (Agentforce product page per entity resolution). Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fathom</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">fathom.ai</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E30" s="3">
+      <c r="E29" s="3">
         <v>5</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Teams of any size ('team of 1 or 1,000') across Sales, Customer Success, Marketing, Operations, HR &amp; Talent, Product &amp; Engineering; team leads and managers</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: No explicit problem statement; implied: note-taking pulls attention from the conversation, things get lost between meetings, and follow-up work eats time</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI notetaking that is out of this world</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Whether you’re a team of 1 or 1,000, Fathom’s got your back</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fathom summarizes your meetings so you can focus on the conversation. Now available bot-free.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get started - free forever</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Whether you’re a team of 1 or 1,000, Fathom’s got your back
 Fathom teams work smarter
 Make your team unstoppable</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fathom gives teams a shared source of truth across every customer conversation, internal sync, and strategy call – so decisions are visible, follow-through is consistent, and nothing gets lost between meetings.</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.fathom.ai/</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched 200, no redirect. Ownership note: site-wide top banner reads "FATHOM IS NOW PART OF SUPERHUMAN." with "LEARN MORE" -&gt; /superhuman (acquisition announcement on page; terms not verified here). H1 verified as the only HTML &lt;h1&gt;; H2 = first body H2; hero paragraph verified verbatim (div.hero_text-block); Primary CTA "Get started - free forever" verified as hero anchor -&gt; https://fathom.video/users/sign_up; Secondary CTA "Not verified" — hero contains one CTA; nav items "Book a Demo" (typeform trigger, href #) and "SIGN UP FREE" excluded as header nav. Section headings verified as HTML &lt;h2&gt; in document order; "Shared visibility. Smarter execution." EXCLUDED (inside w-tab-pane tab content, "Fathom for teams" tab); "Fathom teams work smarter" appears twice (desktop section_teams and section_teams--mobile responsive duplicate) — counted once; its HTML is "Fathom teams&lt;br/&gt;&amp;zwj;&lt;span&gt;work smarter&lt;/span&gt;", recorded with a space in place of the line break and zero-width joiner. Positioning exact sentence from the default-active "Fathom for teams" tab panel (visible on load, but tab content — flagged); ICP "a team of 1 or 1,000" from exact H2; Pain Point "Not verified" — no explicit pain statement on homepage. Vendor claims recorded not endorsed: "Used at 300K+ companies", "95% of users", "6+ hours saved per team member every week on follow-up work", "3X Faster". Other notable copy: "Your meeting data, now inside ChatGPT, Claude, and more"; sales card: "AI Scorecards help managers coach with confidence" (-&gt; /solutions/sales). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: hero contains a single CTA anchor; Pain Point: no explicit pain statement on the homepage or on https://www.fathom.ai/solutions/sales, whose copy is benefit framing). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; sales page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: No comparison, 'only/first/#1', 'why Fathom' or displacement claim in the homepage body (hero, plans, tabs, teams stats, integrations, team-function sections checked). Excluded: footer links 'Fathom vs. Fireflies / Granola / Gong / Otter / Read AI / ZoomMate / Google Meet's Gemini / Built-In Solutions' (footer only; not fetched). Note: hero H1 capture reads 'that is out of this world' (rotating/client-side word likely missing from HTML). Capture: phase2/batches/batch07/captures/fathom_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Otter.ai</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">otter.ai</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E31" s="3">
+      <c r="E30" s="3">
         <v>5</v>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Individuals, teams and enterprises; use-case cards for Sales, Education, Media, Recruiting Agent, SDR Agent; plan copy 'Perfect for individuals and small teams'</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Not stated on the inspected pages; leads with an AI notetaker that goes beyond notes ('Your notetaker should do more than take notes')</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Meeting AI that turns talk into action</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Before, during, and after every meeting.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Transcription. Pre-call briefs. Live coaching. Automatic follow-ups.
 Otter transcribes every meeting, turning it into searchable knowledge that powers your workflow.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start for free</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Schedule demo</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Before, during, and after every meeting.
 Like having your own executive assistant
 Whatever you do, Otter works for you</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Otter transcribes every meeting, turning it into searchable knowledge that powers your workflow.</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'The world's only Conversational Knowledge Engine' (closing CTA section heading)</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://otter.ai/</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched 200, no redirect. H1 ROTATES: the hero contains four HTML &lt;h1&gt; elements inside div.hp_hero-title.is-rollover, in document order: "Meeting AI that turns talk into action" (recorded), "Your notetaker should do more than take notes", "Meeting AI for follow-ups", "Your AI notetaker is now also your Conversational Knowledge Engine"; which displays first is client-side and not confirmed. H2 = first body H2. Hero description = both hero &lt;p&gt; elements verbatim (line break separates them). CTAs verified from hero anchors: "Start for free" -&gt; /signup, "Schedule demo" -&gt; /demo?utm_content=homepagevariant. Section headings verified as HTML &lt;h2&gt; in document order (later sections "Trusted by teams, loved by people" and "Connect to your favorite apps" are H3). Positioning = exact hero paragraph; ICP "Not verified" — homepage addresses multiple audiences (sales, education, media, recruiting agent cards; plan copy "Perfect for individuals and small teams...") with no single explicit ICP statement; Pain Point "Not verified" — no explicit pain statement (closest is rotating H1 "Your notetaker should do more than take notes", a claim rather than a pain statement). Memory-relevant copy verified verbatim: "Have briefing documents delivered before your meeting with all the prior discussions, action items, and updates you need."; "Get real-time, personalized coaching and prompts during calls based on your entire conversation history, company playbooks, and what’s being discussed."; "Key deal details, notes, and next steps automatically extracted from every meeting and synced to your CRM."; "ChatGPT, Claude, and other AI chat tools can securely access your meeting knowledge through Otter’s MCP Server"; SDR Agent card (-&gt; /sdr-agent). Testimonial claim recorded not endorsed: "our team is getting 33% time back". Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (ICP: homepage has no single ICP statement, and https://otter.ai/sales-agent names sales personas 'Account Execs' / 'Sales Ops' / 'Sales Leads' for the sales use case only, not Otter's overall ICP; Pain Point: no explicit pain statement on either page). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row ICP/Pain; Table A Target Buyer; Table B Target Persona/Pain Point; Table C Problem Framing; Table E; sales-agent page); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote is a &lt;div class="heading-style-h2"&gt; (styled as H2, not an HTML &lt;h2&gt;) in the closing CTA section (section.section_cta), present in server HTML. Only one explicit differentiation claim found; customer testimonial 'The most accurate app out there [for transcription].' (testimonials section) not used. Capture: phase2/batches/batch07/captures/otter_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Circleback</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">circleback.ai</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence / meeting automation</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E32" s="3">
+      <c r="E31" s="3">
         <v>4</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Not stated on the inspected pages; logo strip mixes startups, enterprises and universities (Y Combinator, Deloitte, Accenture, Harvard, Stanford); /enterprise page addresses workspace admins; CRM cards imply ops teams</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Meeting knowledge gets lost and note-taking pulls people out of the call: 'Be in the conversation, not in your notes.'; fear of dropped commitments; manual CRM updates after meetings</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Unbelievably good meeting notes</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get the most out of every meeting</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI-powered notes, action items, automations, and search.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get Circleback free</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get the most out of every meeting
 Private and secure
 Connect your favorite apps</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Circleback captures and organizes context from your conversations, so you can focus on what matters most.</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage (the linked /compare page invites comparison but makes no claim of its own: 'See how Circleback’s shared notes, assigned action items, and automations compare with the tools on your shortlist.')</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://circleback.ai/
 https://circleback.ai/compare</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched with curl (HTTP 200, no redirect). H1 verified as the single HTML &lt;h1&gt; in the hero section; H2 = first body H2 ("Get the most out of every meeting"); hero paragraph verified verbatim as &lt;p&gt; directly under the H1; primary CTA "Get Circleback free" verified as HTML anchor (-&gt; /signup) in the hero (same CTA repeated in closing section); secondary CTA "Not verified" — hero contains only one CTA; hero trust links ("500+ testimonials" -&gt; /#testimonials, "Backed by Y Combinator" -&gt; ycombinator.com, "TechCrunch" -&gt; techcrunch.com article) are social-proof badges, not CTAs; header "Log in"/"Sign up" are nav, excluded. Section headings verified as HTML &lt;h2&gt; in document order; feature-card H3s (e.g. "Search across all your meetings"), FAQ H3s and footer H3s excluded. Positioning exact verbatim from &lt;p&gt; under the first H2. ICP "Not verified" — no explicit audience statement in visible homepage body (embedded i18n JSON contains strings such as "What founders say…" and "Most-used deal by YC companies" that were not found as rendered body text, so not used). Pain Point "Not verified" — no explicit vendor pain statement; closest text is a customer testimonial (Siqi Chen, Founder &amp; CEO, Runway: "It gives me a sense of safety that I won’t drop things I owe people.") and closing H2 "Be in the conversation, not in your notes.". Messaging note: the Master Report's "Company Brain" phrase now appears only in &lt;title&gt;/og:title ("Circleback - AI Notetaker, Automations, and Company Brain"); meta description adds "searchable company knowledge" and "connect your AI agents"; body shows HubSpot/Salesforce/Attio integration cards ("Automatically update contacts and deals after meetings"), MCP and CLI integrations ("give AI agents conversation context"), and "Ask questions and get answers drawn from every conversation you’ve had." Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: hero still has a single CTA anchor, 'Get Circleback free'; ICP and Pain Point: no audience statement or vendor pain sentence on the homepage, and the CRO-relevant page https://circleback.ai/enterprise describes admin/security features only; homepage testimonials are client-side skeleton placeholders in the server HTML). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Table A Target Buyer; Table B sections 4-9; Table C; Table E (homepage integration cards, /enterprise)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Differentiation reclassified as Not verified on review: the captured text names or invites a comparison but states no claim. Homepage (batch08/captures/circleback_home.html) has no explicit differentiation claim; only footer links 'Comparisons' (/compare) and 'Alternatives' (/alternatives), excluded as footer. Fetched one named official page linked from the homepage footer, https://circleback.ai/compare (scratchpad capture circleback_compare.html, HTTP 200): quote is the static &lt;p&gt; under &lt;h2&gt; 'Compare with Circleback', followed by 14 'X vs Circleback' cards (Gong, Notion AI, tl;dv, Avoma, Fathom, Fireflies, Granola, Otter, Read AI and others). Weak: names comparison axes but makes no explicit superiority claim. Homepage captured Oct 19, 2026; /compare fetched Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tl;dv</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tldv.io</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Conversation Intelligence</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E33" s="3">
+      <c r="E32" s="3">
         <v>5</v>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Cross-functional teams ('your team') in the hero; coaching section names 'Sales Managers'; footer use cases list Sales Manager, Business Leaders, CS Leaders, CS Reps</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Manual note-taking and post-call data entry: 'Stop wasting time on data entry'; insights lost in unwatched recordings; slow ramp and uneven playbook execution; costly enterprise CI tools</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The AI Notetaker built for Team Collaboration</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tl;dv is trusted by over 2+ million worldwide</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tl;dv is where your team captures knowledge, finds answers, and automates meeting workflows. Any meeting insight, instantly sent to your favourite apps.</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get tl;dv - Free forever</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a Demo</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tl;dv is trusted by over 2+ million worldwide
 Never take meeting notes again - this AI note taker does it for you
 No more manual updates - this AI notetaker handles CRM and follow-ups too</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">tl;dv isn't just for automated note-taking. It's a sales coaching platform powered by artificial intelligence.</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Unlike Gong, which requires a $5,000+ upfront investment, tl;dv provides unlimited meetings, AI-generated notes, and multi-meeting summaries at no cost.' (FAQ answer to 'Is tl;dv free? Try our AI meeting notetaker with no time limits') | 'Leading industry accuracy' (feature label in H2 section 'Transcribe, translate and summarize your meetings in 30+ languages')</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://tldv.io/</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched with curl (HTTP 200, no redirect). The server HTML contains TWO &lt;h1&gt; elements, both class="sr-only" (screen-reader-only); the visible hero headline/subhead are rendered client-side (server HTML shows aria-hidden animate-pulse skeleton placeholders), so visible rendering was not confirmed — H1 recorded as the first sr-only &lt;h1&gt;, Hero Description as the second sr-only &lt;h1&gt; (text verbatim; line break in source collapsed). H2 = first body H2 after EXCLUDING sr-only &lt;h2&gt; "Action Items" (screen-reader label for the hero meeting-card carousel mock-up); primary CTA "Get tl;dv - Free forever" verified as hero anchor (-&gt; /app/login?cta=large-get-tldv); secondary CTA "Book a Demo" verified as hero anchor (-&gt; /contact-sales?utm_source=landing-hero); header duplicates of both and G2 rating link ("4.7(450)") excluded. Section headings verified as HTML &lt;h2&gt; in document order (Section 1 = social-proof logo-strip H2; "2+ million" is a vendor claim). Positioning exact verbatim from coaching-section paragraph (under H2 "Use AI to coach your Sales team - so they sell more, and do it faster."). ICP "Sales Managers" from exact sentence "With AI-driven call analysis, Sales Managers can track playbook adherence, improve objection handling, and gain real-time insights into rep performance." — note homepage is cross-functional (hero addresses "your team"; prompt examples cover Sales, CS, product). Pain Point exact verbatim from &lt;p&gt; under the CRM/follow-ups H2. Also excluded: responsive duplicate spans in H2 "Ready to check tl;dv's impact on your sales team?" (hidden sm:inline / sm:hidden), section.hidden prompt-examples block duplicates, footer H3s. Messaging note: "AI aggregated insights from your company's meetings" and "Multi-Meeting AI Insights" — conversation-scoped memory; footer links "AI Agents for Sales". Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row has no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-16; Table C; Table E (homepage, /teams/sales/sales-managers/)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: static text in &lt;details&gt; FAQ answer under &lt;summary&gt; 'Is tl;dv free? Try our AI meeting notetaker with no time limits' (FAQ H2 'Your note-taking questions, explained'); competitive displacement line naming Gong. Quote 2: &lt;span&gt; feature label under H2 'Transcribe, translate and summarize your meetings in 30+ languages'; unquantified superiority claim. Both in static HTML (batch08/captures/tldv_home.html). Vendor claims, not verified. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Rox</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">rox.com</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Deal Intelligence</t>
         </is>
       </c>
-      <c r="E34" s="3">
+      <c r="E33" s="3">
         <v>2</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Large enterprises: 'the Global 2000' (H1); platform section addresses revenue teams; testimonials from RevOps, CIO and CEO voices</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Not framed as a pain on the homepage; platform page promises to 'consolidate SaaS tools'; testimonial points to rep time lost to admin</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Revenue agents for the Global 2000</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Applied AI research, shipped into revenue growth.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Contact Sales</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start now</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Applied AI research, shipped into revenue growth.
 Automate the entire revenue cycle
 Rox increases pipeline and grows revenue</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">See how the Rox agent can put your pipeline generation, deal management, and account expansion on autopilot.</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Rox Named the Only Visionary in 2026 Gartner® Magic Quadrant™' (announcement banner)</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.rox.com/</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched with curl (HTTP 200, no redirect; Framer site). H1 verified as HTML &lt;h1&gt; ("Revenue agents&lt;br&gt;for the Global 2000" — line break rendered as a space); the H1 sits in a Framer ssr-variant hidden at one breakpoint, where the same slot instead renders a &lt;p&gt; tagline "The Revenue Agent for the Global 2000" (not an H1) — so the H1 wording differs by viewport; &lt;title&gt; = "Rox | Revenue Agents for the Global 2000". H2 = first body H2; repeated Framer breakpoint duplicates of each H2 (e.g. 4x "Applied AI research…", 2x "Automate the entire revenue cycle", 3x "Rox increases pipeline…") not counted separately. Hero Description "Not verified" — hero has no descriptive paragraph (only the H1, CTAs and short testimonial pull-quotes such as ""Rox is how you grow revenue quickly""). Primary CTA "Contact Sales" (-&gt; ./contact) and secondary CTA "Start now" (-&gt; https://run.rox.com/api/auth/login?screen_hint=signup) verified as anchors inside div#contact-ctas in both breakpoint variants; header duplicates excluded. Announcement bar ("Rox named a Visionary in the 2026 Gartner® Magic Quadrant™" -&gt; ./reports/gartner-magic-quadrant) is a vendor/analyst claim, recorded not endorsed, excluded from CTAs. Section headings verified as HTML &lt;h2&gt; in document order; product-card H3s (Agent Workflows, Sales Intelligence, Sales Engagement, Conversation Intelligence, Revenue Intelligence, Account Intelligence) excluded. Positioning exact verbatim from &lt;p&gt; under closing H2 "Get started today". ICP "the Global 2000" from exact H1 text. Pain Point "Not verified" — no explicit pain statement on homepage. Messaging note: no shared-memory language found in homepage body; module list positions Rox as a full revenue suite (incl. Conversation Intelligence). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Hero Description: hero still has no descriptive paragraph, only H1, CTAs and letter-split pull-quotes; Pain Point: no pain statement on the homepage or on https://www.rox.com/platform, whose hero lines 'Automate your revenue and consolidate SaaS tools' / 'From pipeline generation to deal management and expansion' are promises, not pain statements). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-7; Table C; Table E (homepage, /platform)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote: &lt;p&gt; announcement banner above the nav, repeated 3 times in static HTML (desktop/mobile header duplicates, counted once); the page's own body copy beneath reads 'Rox named a Visionary in the 2026 Gartner® Magic Quadrant™' (no 'Only'). Analyst-badge claim recorded verbatim, not verified. No other 'only/first/unlike/vs' claim outside blog-card titles (excluded). Source: batch08/captures/rox_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Humantic AI</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">humantic.ai</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence &amp; RevOps</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E35" s="3">
+      <c r="E34" s="3">
         <v>2</v>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Enterprise sellers and revenue teams on large, complex, multi-stakeholder deals; FAQ names AEs, SAMs, RevOps, Sales Enablement; CRO video section ('Should A CRO Consider Humantic AI?')</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Harder enterprise buying: 'Enterprise buying committees grow bigger, more risk-averse, harder to align.'; point-tool sprawl versus shallow suites; intelligence left in dashboards as 'shelfware'</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Complete Buyer Intelligence.</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To Sell Is Hard. To Buy Is Harder.</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Account, people, visitor, intent and signals, all inside one unified platform instead of five point tools, with depth an all-in-one can't touch.</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start Your Free Trial</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">To Sell Is Hard. To Buy Is Harder.
 Every Single Edge That Your Deal Needs.
 Should A CRO Consider Humantic AI?</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Humantic AI is a Buyer Intelligence platform that combines Account Intelligence (Agent Miia) and People Intelligence (Agent Pi) to help enterprise sellers research accounts, understand stakeholders, and personalize outreach, all at scale and in minutes rather than hours.</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'We coined the term - and built the only platform that makes it possible.' (&lt;p&gt; after stat block, completing 'That's Buyer-First Selling.') | 'Agents Miia and Pi by Humantic AI are purpose-built, multi-agent systems with specialized extractors, domain models, validation layers, and source provenance.' (FAQ answer to H3 'How is Humantic AI different from ChatGPT or generic LLMs?')</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.humantic.ai/</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched with curl (HTTP 200, no redirect; Webflow site). H1 verified as the single HTML &lt;h1&gt; (section.hp2 hero); H2 = first body H2; hero paragraph verified verbatim as &lt;p&gt; under the H1; primary CTA "Start Your Free Trial" verified as the only anchor in div.hp2-cta-row (-&gt; https://account.humantic.ai/?dsb_login=true; label repeated in two spans for hover animation, counted once); secondary CTA "Not verified" — hero has one CTA; navbar "Book Demo" (href="#", JS-handled) and hello-bar "Save Your Seat" (href="#") are outside the hero and not confirmable in HTML. Section headings verified as HTML &lt;h2&gt; in document order — EXCLUDED H2 "Get Your Free Report" (inside div.hi-overlay modal, not a page section) and the H3 widget "Try Agent Pi and Miia for free"; product-card H3s excluded. Positioning exact verbatim first sentence of FAQ answer to "What is Humantic AI?". ICP exact verbatim from FAQ answer to "Who benefits most from Humantic AI? (ICP)". Pain Point exact verbatim from &lt;p&gt; under H2 "To Sell Is Hard. To Buy Is Harder.". Vendor claims recorded not endorsed: H2 "Used By Fortune 10.Gartner Cool Vendor. Taught At Universities.", testimonial metrics (109%, 16.2%). Messaging notes: H2 "Intelligence That Compounds" and "Every visit feeds Miia, Pi &amp; Signals" (Vidar card; Master Report quoted "Miia, Pi &amp; Si" — current text reads "Signals"); H2 "All-In-Ones Are Shallow. Point Tools Are Sprawl."; explicit CRO targeting via H2 "Should A CRO Consider Humantic AI?" and testimonial "Humantic AI is the ultimate edge for CROs"; MCP for agents. &lt;title&gt; = "The Complete Buyer Intelligence Platform For GTM | Humantic AI". Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: div.hp2-cta-row still holds a single anchor; navbar 'Book Demo' is href='#' outside the hero). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 1-13; Table C; Table E (homepage, /start/sales-leader)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: static &lt;p&gt; following &lt;strong&gt; 'Buyer-First Selling' (sentence reads 'That's Buyer-First Selling. We coined the term - and built the only platform that makes it possible.'), just before H2 'Every Single Edge That Your Deal Needs.'. Quote 2: FAQ &lt;p&gt; answer under &lt;h3&gt; 'How is Humantic AI different from ChatGPT or generic LLMs?'. Same FAQ also has displacement line 'Customers switching from competitors like Crystal Knows report higher accuracy, better adoption, and improved deal conversion.' (not used). Source: batch08/captures/humantic_home.html. Vendor claims. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Aligned</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">alignedup.com</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence &amp; RevOps</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence, Content Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E36" s="3">
+      <c r="E35" s="3">
         <v>3</v>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: 'Sales &amp; CS Teams' (H2 under the hero); feature tabs address AEs, champions and enablement; differentiation and testimonials address sales leaders including a CRO</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Deals stall when the seller is absent: 'Stop losing deals between meetings'; most of the buyer journey happens without the seller; CRM blind spots; buyers overloaded with links and attachments</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Stop losing deals between meetings with Aligned AI deal workspace</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">50,000+ Sales &amp; CS Teams Run Their Deals in Aligned</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Run deals in a single shared space where buyers decide faster, and AI agents surface risk, map stakeholders, create content, and guide the next step.</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a Demo</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start free</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">50,000+ Sales &amp; CS Teams Run Their Deals in Aligned
 The Digital Sales Room GTM teams are switching to
 Meet Aligned, Your AI Deal Workspace</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Aligned is the only AI embedded in the buyer-facing workflow. Where sellers work &amp; buyers buy—not in admin tools.</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Aligned is the only AI embedded in the buyer-facing workflow.' (&lt;p&gt; under H2 'The only AI that works where deals actually run') | 'Your CRM Tracks Your Deals. Aligned RUNS them.' (H2)</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://alignedup.com/</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched with curl (HTTP 200, no redirect; WordPress/Elementor site). H1 verified as the single HTML &lt;h1&gt;; H2 = first body H2 (logo-strip claim; "50,000+" is a vendor claim); hero paragraph verified verbatim; primary CTA "Book a Demo" (-&gt; /get-free-demo/) and secondary CTA "Start free" (-&gt; https://my.teamaligned.com/) verified as the anchors immediately after the H1; header "Login"/nav and top webinar banner "Register Now" (-&gt; /webinar-registration) excluded. Section headings verified as HTML &lt;h2&gt; in document order — EXCLUDED H2 "95%" (bare statistic numeral; its statement is the following H3 "of the Buyer Journey Happens When You’re Not in the Room", attributed "*gartner"), so Section 3 = next H2; tab-panel feature headers (rendered as &lt;p&gt; in tabs-side) excluded. Positioning exact verbatim from &lt;p&gt; under H2 "Your CRM Tracks Your Deals. Aligned RUNS them.". ICP "Sales &amp; CS Teams" from exact H2 text (meta description says "50,000+ sales teams"). Pain Point = exact verbatim fragment of the H1 ("Stop losing deals between meetings"), the only explicit pain framing; no standalone pain sentence. Vendor claims recorded not endorsed: "Leader in the 2026 G2 Grid® Reports for Digital Sales Room, and Client Portals for CSMs.", "60%+ enterprise win rate", "-30% reduction in sales cycle". Messaging notes (shared-memory relevance): H2 "Powered by the Aligned Brain™"; "The Brain connects everything that touches your deal and continuously builds a living point of view"; "The Brain already knows your deals"; H2 "Claude and ChatGPT, Now With the Deal Context They're Missing" (MCP: "answers built on real calls, emails, and CRM data"); "AI flags what’s off, explains why it matters, and surfaces deal gaps early"; nav item "Seller Agent New". Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row has no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-12; Table C; Table E (homepage, /revenue-intelligence/)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: static &lt;p&gt; directly under the two-span &lt;h2&gt; 'The only AI that works / where deals actually run'. Quote 2: the &lt;h2&gt; that follows it, contrasting Aligned with the CRM. Also present: hero badges '#1 Digital Sales Room' / '#1 Client Portal' (G2-derived, not used). Source: batch08/captures/aligned_home.html. Vendor claims. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Regie.ai</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">regie.ai</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E37" s="3">
+      <c r="E36" s="3">
         <v>2</v>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Prospecting sellers: /why-regie hero says 'built for sellers'; header mega-menu labels 'For Prospecting Reps' and 'For Founders'; no persona in the homepage hero</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Prospecting busywork crowds out selling: 'Drowning in tasks. Starving for conversations.'; tab-hopping and list prep; generic outreach that earns no replies; guesswork and luck in prospecting</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The fastest path from ICP to pipeline</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Delegate the boring parts of pipeline generation to AI</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RegieGO is an agentic sales workspace with built-in enrichment, emailing, dialing and workflows that gets you prospecting end to end from a single chat.</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start free</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">See how it works</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Delegate the boring parts of pipeline generation to AI
 Show up with a message that moves buyers to act
 Dominate the phone, email and social from one platform</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RegieGO is an agentic sales workspace with built-in enrichment, emailing, dialing and workflows that gets you prospecting end to end from a single chat.</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'The original genAI sales platform, Regie has delivered and analyzed billions of sales messages.' (&lt;p&gt; under H2 'Use AI that already knows the sales game')</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://regie.ai/</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Redirect: https://www.regie.ai/ -&gt; https://regie.ai/ (HTTP 200, 1 redirect). Product now branded "RegieGO" on the homepage (hero paragraph, UI mock labels, nav "Why RegieGO"); &lt;title&gt; "Regie.ai - The AI Sales Assistant for Sellers"; meta description cites "One workspace, $49/mo. Start free." (pricing claim, not endorsed). H1 verified as single HTML &lt;h1&gt; in section.hero-lanes; H2 = first body &lt;h2&gt; ("Delegate the boring parts of pipeline generation to AI"); eyebrow labels ("AI Agents", "Relevant Messaging", "Channel Orchestration", etc.) are &lt;p&gt;, not headings; hero paragraph verified verbatim; primary CTA "Start free" verified from hero HTML anchor (-&gt; https://go.regie.ai/sign-in?ref=home-hero); secondary CTA "See how it works" verified from hero anchor (-&gt; #ai-agents); header "Get a demo" (-&gt; /demo) and "Start free" (-&gt; go.regie.ai/sign-in?ref=header) excluded as nav. Section headings verified as HTML &lt;h2&gt; in document order (first three of five feature-section &lt;h2&gt;s; the remaining two are "Use AI that already knows the sales game" and "Control your own scalable pipeline engine"); footer &lt;h2&gt;s ("Product", "Company", "Resources", "Use Cases") excluded as footer nav. Positioning = hero paragraph (no separate positioning statement). ICP "Not verified" — no body-copy ICP statement; audience labels appear only in the header mega-menu ("For Prospecting Reps Full-cycle AEs, SDRs &amp; founding reps", "For Founders Founder-led selling in a box"), excluded as nav. Pain Point "Not verified" — no explicit pain statement; closest body copy is solution-framed ("Take the guesswork and luck out of prospecting...", "...instead of chasing them."). Shared-memory relevant copy (vendor claim): "Regie learns your voice and your company's pitch, finds the 'why-now' on every account..." and "a tool that gets smarter with each interaction" — wording differs from Master Report quote ("Learns the user's voice and your company pitch"). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: ICP filled from CRO-relevant page https://regie.ai/why-regie hero &lt;p&gt; ('RegieGO is an agentic sales workspace built for sellers.'; no sales-leader/CRO page is linked from the homepage, so /why-regie was used); Pain Point filled from the same page's &lt;h1&gt; 'Drowning in tasks. Starving for conversations.' (followed by 'Half your day goes to tabs and list prep before you say hello to anyone worth talking to.'). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 1-7; Table C; Table E (homepage, /why-regie)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote: static &lt;p&gt; in the 'Sales-Ready AI' section under &lt;h2&gt; 'Use AI that already knows the sales game' (first-mover claim; 'billions' is an unverified vendor metric). Nav link 'Why RegieGO →' excluded as nav; not fetched. Source: batch09/captures/regie_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Quantified</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">quantified.ai</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Content Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E38" s="3">
+      <c r="E37" s="3">
         <v>4</v>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Life sciences and regulated industries ('The #1 Platform for Life Sciences and Regulated Industries', a vendor claim); pharma field teams, with enablement, training, compliance and commercial leaders as buyers</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Traditional roleplay 'is hard to scale, inconsistent across managers'; generic roleplay scores delivery, not compliance; coaching software that 'measures activity' rather than impact</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay That Wins</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Quantified in 2 Minutes</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Smarter Coaching, Faster Readiness, Better Selling, Always Compliant</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get a Demo</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Start a Conversation with Us</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Quantified in 2 Minutes
 Continuous Coaching Across the Full Rep Lifecycle
 The Best AI Roleplay for Life Sciences Teams</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One platform for every stage of the rep lifecycle. Every capability runs on your approved content, your scoring criteria, and one audit trail.</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Generic roleplay tools score how a rep sounds. Quantified is built for regulated environments, so practice reflects your market, your approved claims, and your definition of ready.' ('The Quantified Difference' section, &lt;p&gt; under H3 'Why the World’s Largest Pharma Teams Choose Quantified') | 'Quantified is purpose-built for life sciences and regulated commercial environments, not adapted from horizontal AI.' (FAQ answer to H3 'What makes Quantified different from general-purpose AI tools?')</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.quantified.ai/</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Redirect: https://quantified.ai/ -&gt; https://www.quantified.ai/ (HTTP 200). &lt;title&gt; "AI Sales Coaching &amp; Roleplay Platform for Life Sciences | Quantified". H1 verified as HTML &lt;h1&gt; ("Wins" wrapped in span.text-span); hero sub-line verified as &lt;p class="home-hero-sub"&gt; (used as Hero Description); H2 = first body &lt;h2&gt; (literal HTML "Quantified&lt;br/&gt;in 2 Minutes" — &lt;br&gt; rendered as a space; same treatment for "The Best AI Roleplay&lt;br/&gt;for Life Sciences Teams"); primary CTA "Get a Demo" verified from hero anchor (-&gt; /demo-request); secondary CTA "Start a Conversation with Us" verified as hero anchor a.hero-floater-2 (floating avatar card over hero video, -&gt; /demo-request, same destination as primary; small label "Quantified" above it excluded); header "Login"/"Get a Demo" excluded as nav. Section headings verified as HTML &lt;h2&gt; in document order; mega-menu promo text and w-tab-pane &lt;h3&gt;s ("New Hire Onboarding" etc.) excluded as nav/tab content. Positioning verbatim from div.medium-text under "Continuous Coaching Across the Full Rep Lifecycle" — note wording now "one audit trail" (Master Report quoted "one comprehensive data foundation"; no longer on page). ICP from logo-strip &lt;strong&gt; "The #1 Platform for Life Sciences and Regulated Industries" ("#1" is a vendor claim, not endorsed); also FAQ sub "life sciences and commercial leaders". Pain Point verbatim first sentence of FAQ answer "How is AI roleplay different from traditional sales roleplay?"; also "Generic roleplay tools score how a rep sounds." Vendor claims recorded not endorsed (FAQ: "up to a 40% reduction in time to readiness, up to 6× more rep practice"; "Sanofi certified 100% of its 500-rep field force"). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row had no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 1-13; Table C; Table E (homepage FAQ, /platform/ai-insights-agent)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: static &lt;p&gt; in section labelled 'The Quantified Difference' under the two-&lt;h3&gt; heading 'Why the World’s Largest / Pharma Teams Choose Quantified'. Quote 2: first sentence of FAQ &lt;p&gt; answer under &lt;h3&gt; 'What makes Quantified different from general-purpose AI tools?'. Also present: &lt;strong&gt; 'The #1 Platform for Life Sciences and Regulated Industries' (between 'Start a Conversation with Us' and 'See It in Action', not used). Source: batch09/captures/quantified_home.html. Vendor claims. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PitchMonster</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">pitchmonster.io</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E39" s="3">
+      <c r="E38" s="3">
         <v>5</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: 'sales teams' (hero paragraph); problem, setup and FAQ sections address sales leaders, managers and enablement; use-case slider adds CS and recruiters</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Reps practise on live buyers: 'Most sales teams are still practising on real customers'; no structured coaching; manual call reviews that do not scale; long ramp</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Role-play</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Practice before the call. Coach after it. Repeat.</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PitchMonster helps sales teams practice real conversations, analyze live calls, and get AI coaching – before and after every deal.</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a Demo</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Practice before the call. Coach after it. Repeat.
 Training for every stage of the sales cycle
 Built around your sales process</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PitchMonster helps sales teams practice real conversations, analyze live calls, and get AI coaching – before and after every deal.</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'PitchMonster is the only AI sales roleplay platform in the top 5 – built for teams where data residency and compliance aren’t optional.' (&lt;p&gt; under H2 'Built for teams that need to move fast and stay compliant') | 'No competitor has this right now.' (FAQ answer to 'How is PitchMonster different from other AI sales roleplay software?')</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.pitchmonster.io/</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">No redirect (HTTP 200). H1 verified as HTML &lt;h1&gt; composed of spans "AI " + inline decorative SVG + "Sales " + "Role-play" (recorded as "AI Sales Role-play"); subhead "With Instant AI Coaching" verified as span text in div.hero-subhead (not a heading, not counted); H2 = first body &lt;h2&gt; (literal "Practice &lt;span&gt;before the call.&lt;/span&gt;&lt;br/&gt;Coach after it. Repeat."); hero paragraph verified verbatim (p.hero-body); primary CTA "Book a Demo" verified from hero anchor a.cta-hero (-&gt; /book-a-demo); secondary CTA "Not verified" — hero contains only one CTA (header "Book a Demo" desktop/mobile duplicates excluded as nav). Section headings verified as HTML &lt;h2&gt; in document order; use-case slider &lt;h3&gt;s repeated 3x (carousel clones) and AI-tools tab buttons excluded. ICP "sales teams" from hero paragraph; trust strip says "Trusted by 300K+ reps from World’s leading teams" (vendor claim; Master Report cited 30,000+). Pain Point verbatim from body &lt;h3&gt; "Most sales teams are still practising on real customers" (followed by "= Deal lost." and cards e.g. "Manual reviews don't scale"). Other vendor claims recorded not endorsed: "PitchMonster is the only AI sales roleplay platform in the top 5", "Enterprise clients renew at 100%". Content-grounding copy relevant to PitchSense: "Create role-plays from your product docs, real calls, transcripts, and your website."; "Connect Salesforce and Gong to build role-plays in seconds from your live deal data". Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA re-checked: the hero contains a single anchor, 'Book a Demo'; the other 'Book a Demo' anchors are header desktop/mobile copies). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-12; Table C; Table E (homepage, /solutions/sales-leaders)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1: static &lt;p&gt; in 'Enterprise ready' section under two &lt;h2&gt;s 'Built for teams that need' / 'to move fast and stay compliant' ('top 5' ranking unspecified). Quote 2: last sentence of FAQ &lt;p&gt; answer under question &lt;span&gt; 'How is PitchMonster different from other AI sales roleplay software?' (preceding sentences: AI Coach that asks leading questions vs a score after a role-play). Source: batch09/captures/pitchmonster_home.html. Vendor claims. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Wonderway</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">wonderway.io</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Call Intelligence, Coaching Intelligence</t>
         </is>
       </c>
-      <c r="E40" s="3">
+      <c r="E39" s="3">
         <v>2</v>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: 'remote sales teams' (hero copy); product and differentiation sections address sales leaders, enablement and sales managers</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Performance gaps and dropped deals the team cannot see: 'Stop losing winnable deals' (CRO page); long ramp; coaching that does not reach every call</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Boost sales performance through learning</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get up and running fast. Instant access, fast results.</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Drive sales onboarding and sales upskilling, coach and certify remote sales teams with all-in-one sales LMS that integrates easily into your sales tech stack.</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are in a good company
 The All-in-One Data Driven Sales LMS
 Real sales coaching on EVERY. SINGLE. CALL.</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sales performance platform proven to increase the revenue per rep with the right sales training.</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage (only section labels: 'What makes us different?' and 'Why successful sales teams choose Wonderway', with no claim beneath them)</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.wonderway.io/</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">No redirect (HTTP 200). Page uses &lt;h1&gt; for 8 headings; H1 recorded = hero &lt;h1&gt; "Boost sales performance through learning" (inside a single-slide w-slider; eyebrow "Data-Driven Sales Training Platform" is a div). H2 = first &lt;h2&gt; in document order ("Get up and running fast. Instant access, fast results."). Hero paragraph verified verbatim. CTAs "Not verified": hero anchors "Book a demo" (-&gt; /demo-request-main), "Watch video" and "Watch Demo" (-&gt; /watch-demo-registration) exist in HTML but their container div.div-block-369 carries class "hide", and the site stylesheet (wonderway.shared.8d4ac4f95.min.css) defines .div-block-369.hide{display:none} — not visible; header "Book demo" and closing "Request a demo"/"See how it works" also hidden via .hide. Visible CTAs elsewhere: "Sign up for Free" (-&gt; /wonderway-coach-ai-old, AI Coach section) and banner "Register for Free &gt;&gt;&gt;" (-&gt; summit.wonderway.io). Section headings = section-level headings after hero in document order (all HTML &lt;h1&gt;, not &lt;h2&gt;): logos section, LMS section, AI Coach section (literal "Real sales coaching on&lt;br/&gt;EVERY. SINGLE. CALL."); feature-card &lt;h3&gt;s excluded. AI Coach section still labelled "Beta release of our revolutionary AI-powered Coach is live!". Positioning verbatim from footer paragraph (footer-side, visible). ICP "remote sales teams" from hero paragraph. Pain Point "Not verified" — no explicit pain statement; Master Report's "Stop losing winnable deals" not found in captured HTML. Rebrand signal: hidden footer column and nav reference "Verity by BTS" (AI coach, logo "Verity by BTS TM") and "Login Verity" (alpha.wonderway.io); success-story link "Verity- Combe Grove" — suggests AI coach now marketed as Verity by BTS (relationship not stated on page). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: Pain Point filled from CRO-relevant page https://www.wonderway.io/sales-intelligence-software closing-section &lt;h2&gt; 'Stop losing winnable deals' (sub-line 'Improving your team's win rate is the easiest way to unlock revenue in a downturn'; that page shows legacy-template signals: logo links to /old-home, nav Pricing to /pricing-old, a lorem-ipsum paragraph in a tab panel); Primary/Secondary CTA stay Not verified (hero anchors re-checked: container div.div-block-369 carries class 'hide'). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 3-8; Table C; Table E (homepage, /sales-intelligence-software)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Differentiation reclassified as Not verified on review: the captured text names or invites a comparison but states no claim. Quote 1: &lt;div&gt; eyebrow repeated above three feature &lt;h1&gt;s ('Skill profiles that identify areas for improvement', 'Targeted sales training recommendations', 'See the impact of sales training and coaching on revenue'). Quote 2: &lt;strong&gt; inside &lt;h1&gt;, answered by 'Super fast implementation', 'Dedicated sales enablement consultant', 'Customisation for your organisation'. Weak: section labels only, no claim against named alternatives. Footer links to 'Verity by BTS' noted for entity check. Source: batch09/captures/wonderway_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PathFactory</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pathfactory.com</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+    <row r="40" ht="90" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mediafly</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mediafly.com</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sales Enablement &amp; Content Intelligence</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Content Intelligence</t>
-        </is>
-      </c>
-      <c r="E41" s="3">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: B2B marketing and sales teams: 'Enable sales and marketing' (ABM card); solutions address ABM, demand gen and web teams; hero names the end audience as 'self-serve buyers'</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Content operations and shallow measurement: 'Stop building hundreds of one-off pages.'; clicks and lead scores that hide buying intent; content not tied to pipeline</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Right Content. Right When Buyers Need It.</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trusted by the world's leading companies</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PathFactory uses AI to deliver personalized content experiences for self-serve buyers, at scale, while capturing first-party engagement data that drives revenue.</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">See it in action</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deal Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
+        </is>
+      </c>
+      <c r="E40" s="3">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Revenue teams: 'How Mediafly Empowers Your Revenue Team' (H2); nav By role lists Revenue Leaders, Marketing Leaders, Customer Success Leaders</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Complex multi-product selling: 'Stalled deals, missed quotas, and longer sales cycles.'; scattered content, disconnected tools, inconsistent messaging and low seller adoption; reps telling different value stories</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The only sales enablement platform with value selling tools built in</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trusted by leading enterprise organizations</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powered by AI, so all your reps tell the same value story, with the same content and quantification of impact.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a demo</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trusted by the world's leading companies
-An Intelligent Way to Enable Buyer Education
-An Intelligent Way to Win</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PathFactory unifies experiences, engagement, and intelligence into one platform, so every buyer journey is personalized, connected, and measurable.</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.pathfactory.com/</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No redirect (HTTP 200). Acquisition: homepage banner states "PathFactory has been acquired by Kaltura, the leading enterprise video and digital experience platform. Together, we're building the future of AI-powered content intelligence and personalized digital experiences." ("Learn more" -&gt; corp.kaltura.com/landing_pages/general/welcome-pathfactory/); banner text is &lt;p&gt;, not a heading. H1 verified as HTML &lt;h1&gt;; H2 = first body &lt;h2&gt; (logo strip); hero paragraph verified verbatim; primary CTA "See it in action" verified from hero anchor styled bg-primary (-&gt; nurturenow.pathfactory.com Navattic product tour, opens new tab); secondary CTA "Book a demo" verified from hero anchor styled bg-secondary (-&gt; /demo); header "Book a demo" excluded as nav. Section headings verified as HTML &lt;h2&gt; in document order; card &lt;h3&gt;s and integrations filter buttons excluded; later &lt;h2&gt;s "The Intelligent Journey Platform", "Connect Your Entire Revenue Stack". Positioning verbatim from paragraph under "The Intelligent Journey Platform". ICP "sales and marketing" from ABM card "Enable sales and marketing to initiate and guide personalized buying experiences using content intelligence." (no dedicated ICP statement; meta/title target B2B). Pain Point verbatim from &lt;h3&gt; card "Build Once. Let AI Personalize Everywhere." body; also "Go beyond clicks and lead scores." Platform includes "ChatFactory: AI Buying Agents" (card heading only). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (row had no Not-verified fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-9; Table C; Table E (homepage, /platform/intelligence/)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: No 'only/first/unlike/#1/vs', comparison, 'why PathFactory' or FAQ section in static HTML (batch09/captures/pathfactory_home.html). Nearest contrast lines, not counted as explicit claims: 'Go beyond clicks and lead scores.' (p under H3 'Connect Every Engagement to Revenue') and 'Stop building hundreds of one-off pages.' (p under H3 'Build Once. Let AI Personalize Everywhere.'). Kaltura acquisition banner present. No 'why'/comparison page linked from the homepage, so none fetched. Homepage captured Oct 19, 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uniphore</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uniphore.com</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deal Intelligence, Shared Memory</t>
-        </is>
-      </c>
-      <c r="E42" s="3">
-        <v>2</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Large enterprises: 'the world’s most demanding businesses'; value pillars address enterprise AI and IT leaders; sales appears only in the 'Sales and Revenue Ops' use-case card and the Revenue Operations page</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Enterprise AI stuck between pilot and production: 'the tool sprawl that slows down most enterprises'; costly frontier-model calls and vendor lock-in; RevOps page cites unused seller data and 'gut-feel' forecasts</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not verified</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Redefining Enterprise Intelligence with Autonomous AI</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not verified</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Get the Insights</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not verified</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Frontiers of Enterprise AI
-Flywheel of Intelligence Built for Your Business
-Uniphore Business AI Cloud</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">End-to-End AI Platform for Enterprises Combining Data, Models and Agents</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'A unified platform that compounds intelligence across your stack, unlike point solutions that start from zero' ('The Frontiers of Enterprise AI' section, card H3 'Compounding Intelligence') | 'with a platform-first approach instead of the tool sprawl that slows down most enterprises' ('The Frontiers of Enterprise AI' section, card H3 'AI Adoption Velocity')</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uniphore.com/</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fetched https://www.uniphore.com/ (HTTP 200, no redirect; &lt;title&gt; "Uniphore | The Business AI Company"). H1 "Not verified" — the saved HTML contains NO &lt;h1&gt; element (0 occurrences). Hero is a 4-slide auto-rotating slick carousel (autoplay 6000ms, fade); slide text is in &lt;p&gt; elements except slide 0. H2 = first body H2 "Redefining Enterprise Intelligence with Autonomous AI", verified as &lt;h2&gt; inside the default-visible slide 0 (div#sliderTextSpec-0.slideTextAndBtn.show, eyebrow &lt;p&gt; "MIT Technology Review Insights Report") — a report promo, not a product statement. Other slides (all &lt;p&gt;, recorded for context): slide 1 "INTRODUCING UNIPHORE MARKETING AI" / "Moving Marketing Beyond the CDP" (CTA "Explore Marketing AI" -&gt; /platform/business-ai-cloud/marketing-ai/); slide 2 "End-to-End AI Platform for Enterprises Combining Data, Models and Agents" (CTA "Explore the platform" -&gt; /platform/business-ai-cloud/); slide 3 "Business AI. Business Outcomes." + "Uniphore Business AI Cloud takes organizations from AI experimentation to measurable, production-grade outcomes" (CTA "Learn how KPMG did it" -&gt; /customers/global-advisory-firm/). Hero Description "Not verified" — default slide 0 has no descriptive paragraph and slides rotate, so no single fixed hero description exists. Primary CTA "Get the Insights" verified as a.btn.cs-button in slide 0 (-&gt; https://www.uniphore.com/resources/analyst-reports/redefining-enterprise-intelligence-with-autonomous-ai/); Secondary CTA "Not verified" — each slide carries a single CTA; header "Contact us" (-&gt; https://www.uniphore.com/contact/) is a nav button and not counted. Section headings verified as &lt;h2&gt; in document order after the hero ("What we Unlock" / "WHAT WE DO" / "HOW WE DO IT" are eyebrow &lt;p&gt;, not headings); mega-menu promo text ("Uniphore Business AI Cloud", "Unify data, knowledge, models, and agents to power AI execution" — &lt;p&gt; inside header nav) excluded. Positioning exact verbatim from carousel slide 2 &lt;p&gt;. ICP from exact homepage paragraph "From global banks to leading insurers, the world’s most demanding businesses deploy Uniphore and scale fast" (under H2 "The World’s Most Demanding Organizations Trust Uniphore"). Pain Point exact substring of the "AI Adoption Velocity" paragraph: "The ability to move from first deployment to measurable business value, with a platform-first approach instead of the tool sprawl that slows down most enterprises". Stats labels ("Fortune 500 companies running Uniphore in production", "Businesses worldwide across 20+ countries...") present but numeric values are not in static HTML text — not recorded. Sales relevance limited to use-case card "Sales and Revenue OpsAI-assisted pipeline management, forecasting, and deal execution at scale."; homepage messaging is enterprise-wide Business AI (data/knowledge/model/agent layers, "Compounding Intelligence", "knowledge graph", "context graph") with a new Marketing AI launch; vendor claims (Gartner MQ Leader for CDPs, awards) recorded as claims only. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (H1: the homepage HTML still has no &lt;h1&gt;; Hero Description: default slide 0 has no descriptive paragraph and slides rotate; Secondary CTA: each slide carries a single CTA. The Revenue Operations page https://www.uniphore.com/use-cases/front-office/revenue-operations/ was checked but cannot supply homepage hero fields). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-12; Table C; Table E (Revenue Operations page)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: Quote 1 is a &lt;p&gt; under H3 'Compounding Intelligence' and quote 2 is part of a &lt;p&gt; under H3 'AI Adoption Velocity' ('The ability to move from first deployment to measurable business value, with a platform-first approach...'), both in the H2 'The Frontiers of Enterprise AI' section; both in static HTML. Excluded: 'Recognized as a Leader' / '2026 Magic Quadrant Leader' and award badges (analyst/award badges, vendor claims, not a comparison with alternatives). Capture: phase2/batches/batch10/captures/uniphore_home.html. Homepage captured Oct 19, 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Level AI</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thelevel.ai</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conversation Intelligence (contact center)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call Intelligence, Coaching Intelligence, Shared Memory</t>
-        </is>
-      </c>
-      <c r="E43" s="3">
-        <v>4</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Contact-center and CX operations: 'teams running high-volume, high-stakes customer operations'; nav roles Contact Center Leaders, Agents, CX Leaders</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Customer signals not acted on across the business; manual call-by-call review; general-purpose LLM wrappers framed as less accurate and costlier; Sales Performance page: 'Unlock hidden revenue in every deal'</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Full stack AI agents for the entire customer experience journey</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helping teams improve</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deploy AI agents for automation, intelligence and quality at enterprise scale. Built on CX specific full stack AI.</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Get a demo</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">See AI models</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Helping teams improve
-Win on customer experience
-Equip your team to do their best work</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manage all CX operations on a single platform of shared intelligence</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'7 domain-specific models handle specialized tasks with higher accuracy, a fraction of the cost, and more control than general-purpose LLM wrappers.' ('why level ai' section, card 'Proprietary CX intelligence') | 'The AI with the most customer experience' ('why level ai' section H3)</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://thelevel.ai/</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fetched https://thelevel.ai/ (HTTP 200, no redirect; Framer site; &lt;title&gt; "AI + human intelligence through the full customer journey | Level AI"). H1 verified as HTML &lt;h1&gt; in the desktop SSR variant (div.ssr-variant.hidden-1j2wscr.hidden-i1gfjr); the same text appears twice more as &lt;h2&gt; in the tablet/mobile SSR variants — responsive duplicates, excluded. Hero paragraph verified verbatim (also duplicated across variants). Eyebrow "4.7 (200+ reviews)" is a &lt;p&gt;, not a heading; top banner "Level Up 2026: Nov 4–6, Hayes Mansion, San Jose. Spots are limited" / "Join the waitlist" is an event banner, not hero. CTAs verified from HTML anchors: "Get a demo" -&gt; ./request-demo (https://thelevel.ai/request-demo); "See AI models" -&gt; ./product/one-ai-platform. H2 = first non-duplicate body H2 "Helping teams improve"; it is followed by rotating industry-label H2s (Financial Services, Healthcare, Retail, Insurance, Consumer Tech, Enterprise SaaS, Contact Centers, Ecommerce, Financial Services) — animated word-cycle fragments, excluded. Case-study "Read story" carousel (repeated 3x) and testimonial quotes excluded. Section headings verified as &lt;h2&gt; in document order; "Win on customer experience" and "Equip your team to do their best work" each appear twice (responsive duplicates, counted once). Later H2s: "Turn every interaction into action", "Seven task-specific models for customer experience", "Built for the complexity of enterprise CX", "Integrates with the tools you already use", "Frequently Asked Questions". Positioning exact verbatim from paragraph under "Equip your team to do their best work". ICP from exact paragraph "Level AI is the strategic partner for teams running high-volume, high-stakes customer operations. From strategy to production deployment, we help you build your operating model." Pain Point "Not verified" — no explicit pain-point statement; closest copy ("Your customers tell you what they need, what's broken, and where there's risk.") describes customer signals, not a buyer pain. Shared-memory-relevant copy: "Human and AI agents act from the same intelligence, rubrics, and learning"; "Every human and AI interaction compounds into calibration and training for the next one."; "Connect every customer signal into one intelligence layer for resolution, quality, and CX improvement." Vendor claims recorded as claims: "+25% CSAT", "3x CONTAINMENT", "Up to 49x more cost efficient, 4x faster", "Trusted by global enterprises serving 1B+ people, 10B+ annual touchpoints, and $500B in market cap". Contact-center/CX scope; no sales-team messaging. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Pain Point: no explicit pain-point statement on the homepage or on the Sales Performance page https://thelevel.ai/solutions/sales-performance; its copy states goals such as "decrease the gap between top and bottom performers", not a buyer pain). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-11; Table C; Table E (homepage, Sales Performance page)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: Both quotes sit in the section labelled 'why level ai' (eyebrow &lt;p&gt;) under H2 'Built for the complexity of enterprise CX': quote 1 is the &lt;p&gt; under card label 'Proprietary CX intelligence'; quote 2 is an &lt;h3&gt; followed by an animated counter (digit spans; the counter value is client-side animation and was not recorded). Framer SSR markup; responsive duplicates excluded. Comparative performance figures ('Up to 49x more cost efficient, 4x faster') are vendor claims and not used. Capture: phase2/batches/batch10/captures/levelai_home.html. Homepage captured Oct 19, 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balto</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">balto.ai</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conversation Intelligence (contact center)</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Call Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
-        </is>
-      </c>
-      <c r="E44" s="3">
-        <v>5</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: 'contact centers' (hero paragraph), including sales, CX and compliance-driven centers; review-wall filters name Agent, Manager, Executive</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Agents cannot hold every answer in the moment; sampling-based QA gives a partial view ('replace sampling with certainty'); rigid IVR menus</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Agent Assist | QA Automation | Agentic Insights] Wrapped into a single platform</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loved by customers. Proven against competitors.</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">One unified system where humans and AI collaborate to drive quality, efficiency, and revenue for contact centers</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Get a demo</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proven ROI</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loved by customers. Proven against competitors.
-Trusted by 300+ leading customers where sales, CX, &amp; compliance matter
-Proven ROI across every contact center metric</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balto is an AI platform that integrates directly with your existing phone systems. It listens to conversations in real time, provides real-time guidance to agents, automates coaching and QA, and deploys fully automated AI voice agents, all from a single platform.</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'Unlike traditional IVR systems that rely on rigid menus and scripts, Balto's AI voice agent, Togo, uses large language models trained on your best agent conversations.' (FAQ answer to 'How does Balto's AI voice agent differ from a traditional IVR?') | 'Help every agent perform like your best with the most advanced agent assist' ('One platform. Every interaction, elevated.' section, Agent Assist card)</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.balto.ai/</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fetched https://www.balto.ai/ (HTTP 200, no redirect; &lt;title&gt; "Balto | Contact Center AI Software | Balto"). H1 verified as HTML &lt;h1&gt; but ROTATES: it contains span.hero-cycle-wrap with three span.hero-cycle-word items ("Agent Assist", "QA Automation", "Agentic Insights") followed by static text "Wrapped into a single platform"; recorded with the rotating words in brackets separated by "|" (brackets/pipes are notation, not page text). Hero paragraph verified verbatim (p.hero-sub). CTAs verified from HTML anchors in div.hero-cta: "Get a demo" (a.btn.btn-primary -&gt; /get-demo/) and "Proven ROI" (a.btn.btn-ghost -&gt; #proven-roi, an in-page anchor, not a conversion page). H2 = first body H2 "Loved by customers. Proven against competitors." (review wall; tab buttons All reviews/Agent/Manager/Executive and review cards excluded). Section headings verified as &lt;h2&gt; in document order; later H2s: "One platform. Every interaction, elevated.", "Built to work with the system you already rely on", "Designed to meet the highest security standards", "FAQs", "Ready to transform your contact center?". Positioning exact verbatim from the first FAQ answer &lt;p&gt;. ICP "contact centers" from the hero paragraph (exact text "...for contact centers"); industries also named in "Balto is built for the industries where security is non-negotiable, healthcare, financial services, and beyond." Pain Point "Not verified" — no explicit vendor pain-point statement; the Master Report's "can't memorize all scenarios" comes from a customer review card ("It is time sufficient &amp; very useful since we are unable to memorize all scenarios[...]" — Benedict V., Sr. Customer Service Assistant), not vendor copy, so not used. Vendor claims recorded as claims: "300+ customers", "Most customers are live within 30 days", "prebuilt integrations with over 60 providers". Notable: product cards include an AI voice agent named "Togo" and "AI coaching recommendations ... directly linking them to outcomes"; contact-center scope, not B2B sales teams. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Pain Point: no explicit vendor pain-point statement on the homepage or on the Insights page https://www.balto.ai/contact-center-insights/; "replace sampling with certainty" in the QA/QM card implies a pain but does not state one). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-10; Table C; Table E (homepage, Insights page)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: Quote 1 is the first sentence of the &lt;p&gt; answer under FAQ question span 'How does Balto's AI voice agent differ from a traditional IVR?' (H2 'FAQs'); quote 2 is the &lt;p&gt; under the 'Agent Assist' label in the H2 'One platform. Every interaction, elevated.' section; both in static HTML (FAQ answer is in an accordion, present in HTML). Excluded: nav link 'Balto vs Competitors' (navigation, not page copy). Capture: phase2/batches/batch10/captures/balto_home.html. Homepage captured Oct 19, 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mediafly</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mediafly.com</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sales Enablement &amp; Content Intelligence</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deal Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
-        </is>
-      </c>
-      <c r="E45" s="3">
-        <v>5</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Revenue teams: 'How Mediafly Empowers Your Revenue Team' (H2); nav By role lists Revenue Leaders, Marketing Leaders, Customer Success Leaders</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Complex multi-product selling: 'Stalled deals, missed quotas, and longer sales cycles.'; scattered content, disconnected tools, inconsistent messaging and low seller adoption; reps telling different value stories</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The only sales enablement platform with value selling tools built in</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trusted by leading enterprise organizations</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Powered by AI, so all your reps tell the same value story, with the same content and quantification of impact.</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Book a demo</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Explore by solutions</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Trusted by leading enterprise organizations
 How Mediafly Empowers Your Revenue Team
 Latest insights</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Unify content management, value selling and realization, learning and coaching in one platform, so every team works from the same resources, scales effortlessly, and drives growth together.</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'The only sales enablement platform with value selling tools built in' (hero H1)</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mediafly.com/</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched https://www.mediafly.com/ (HTTP 200, no redirect; Elementor site; &lt;title&gt; "Sales Enablement &amp; Content Management Platform | Mediafly"). H1 verified as HTML &lt;h1&gt; (markup "The &lt;i&gt;only s&lt;/i&gt;ales enablement platform &lt;br&gt;with value selling tools built in" — italic span and line break are styling; rendered text recorded). Hero Description = &lt;h5&gt; subheading directly under the H1, verified verbatim (line break removed). Primary CTA "Book a demo" verified as a.elementor-button directly under the H5 (-&gt; https://www.mediafly.com/demo). Secondary CTA "Explore by solutions" verified as a.elementor-button (-&gt; https://www.mediafly.com/solutions) in the adjacent hero container next to the "Unify content management..." paragraph; a third button "Explore by teams" (-&gt; https://www.mediafly.com/solutions/#revenue-engine) not counted. Header nav buttons "See us in action" (-&gt; /demo) and "Log in" (-&gt; viewer.mediafly.com) excluded as nav. Page has only two H2s, both recorded; Section Heading 3 is the next heading in document order, &lt;h3&gt; "Latest insights" (resource cards). H4 product cards (Engagement, Value, Learning &amp; Coaching, Services) and responsive tab/desktop/mobile H4 assessment prompts excluded. Positioning exact verbatim from the hero-container &lt;p&gt;. ICP "Revenue Team" exact from H2 "How Mediafly Empowers Your Revenue Team"; reinforced by "Command Center is Mediafly’s built-in AI assistant and orchestration layer for revenue teams." Pain Point "Not verified" — no explicit pain statement in page copy; a resource-card link title "Eliminate Revenue Enablement Platform Sprawl &amp; Maximize AI-driven Growth" is a blog headline, not homepage messaging, so not used. Notable: Command Center AI assistant "enables sellers to find the right information and prepare for customer conversations, all within Mediafly Engagement’s proven governance and permissions structures"; Services copy mentions "designing governance and rollout plans for AI and agents". Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: Pain Point filled from the Revenue Leaders page https://www.mediafly.com/solutions/revenueleaders/ (the &lt;p&gt; in the "Problem" tab panel under H2 "Revenue enablement for enterprise organizations"; tab content present in static HTML; the homepage has no explicit pain statement). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-6; Table C; Table E (homepage, Revenue Leaders page)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote is the hero &lt;h1&gt;; markup 'The &lt;i&gt;only s&lt;/i&gt;ales enablement platform &lt;br&gt;with value selling tools built in' — italic tag and &lt;br&gt; are styling, so the quote matches after removing inline tags (rendered text). No second explicit differentiation claim on the page; 'Why choose Mediafly' appears only as a mega-menu label (excluded). Capture: phase2/batches/batch10/captures/mediafly_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="90" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="41" ht="90" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SalesHood</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">saleshood.com</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Content Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E46" s="3">
+      <c r="E41" s="3">
         <v>4</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: 'enablement teams' (under H2 'Activate your repeatable revenue engine'); hero addresses 'every seller'; leaders get buyer-engagement visibility; CRO and revenue-leader testimonials</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: No explicit pain on the homepage; implied gap between enablement and consistent execution ('Turn sales enablement into repeatable sales execution'); Impact Insights page cites pipeline health and forecast accuracy</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Revenue enablement at AI speed</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Turn sales enablement into repeatable sales execution</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Our purpose-built AI builds training from your content, coaches every seller with role play, and shows the results, from certified sellers to engaged buyers.</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Book a demo</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">See Platform</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Turn sales enablement into repeatable sales execution
 Activate your repeatable revenue engine
 Develop sellers who execute with confidence</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Everything your sales enablement team runs, in one platform: content management, training and onboarding, AI coaching and role play, guided selling, and digital sales rooms.</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Rated best results and best usability' (H3 above testimonials)</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://saleshood.com/</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Fetched https://www.saleshood.com/ — 1 redirect to https://saleshood.com/ (HTTP 200; Elementor site; &lt;title&gt; "SalesHood | AI-Powered Revenue Enablement Platform"). H1 verified as HTML &lt;h1&gt; (markup "Revenue enablement&lt;br /&gt;&lt;span&gt;at &lt;em&gt;AI&lt;/em&gt; speed&lt;/span&gt;" — line break rendered as a space). Hero paragraph verified verbatim (text-editor div directly under H1). CTAs verified from HTML anchors: "Book a demo" (-&gt; https://saleshood.com/demo/) and "See Platform" (-&gt; /platform-tour/). Hero proof line "4.6-star rating from 828 verified G2 reviews. Fall 2026 G2 Leader." is a &lt;p&gt; (vendor claim, not a heading). H2 = first body H2; section headings verified as &lt;h2&gt; in document order; fourth H2 "Turn buyer engagement into revenue insight" and closing H2 "Schedule a demo" not used; H4 card links ("Take a platform tour", "Explore our platform", "Book a demo") and H3s ("SalesHood integrates seamlessly with all your existing applications.", "Rated best results and best usability") excluded as sub-elements. Positioning exact verbatim from paragraph under the first H2. ICP "enablement teams" from exact paragraph "Give enablement teams the tools and AI capacity to create, organize, and launch the programs, content, and guidance that help sellers execute consistently." Pain Point "Not verified" — no explicit pain-point statement on homepage. Customer quotes recorded as claims only (e.g. "We boosted win rates and cut sales cycles by 35% with SalesHood."; "With SalesHood, we’re rolling out new GTM programs every six weeks instead of twice a year."). Notable for PitchSense: hero promises AI that "builds training from your content" and leader "visibility into buyer engagement, seller readiness, and what drives performance" (paragraph under "Turn buyer engagement into revenue insight"). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Pain Point: no explicit pain-point statement on the homepage or on the Impact Insights page https://saleshood.com/sales-enablement-platform/impact-insights/). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-10; Table C; Table E (homepage, Impact Insights page)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote is an &lt;h3&gt; introducing the customer testimonial block (third-party rating claim, recorded not endorsed). No 'only/unlike/vs' copy in the page body. Excluded: hero badge text '4.6-star rating from 828 verified G2 reviews. Fall 2026 G2 Leader.' (analyst badge) and footer/nav links 'Why SalesHood', 'Highspot Alternative', 'Seismic Alternative' (comparison pages exist at /why-saleshood/, /highspot-alternative/, /seismic-vs-saleshood/ but were not fetched since the homepage holds a claim). Capture: phase2/batches/batch10/captures/saleshood_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="90" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="42" ht="90" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yoodli</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">yoodli.ai</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI Sales Coaching &amp; Roleplay</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Coaching Intelligence</t>
         </is>
       </c>
-      <c r="E47" s="3">
+      <c r="E42" s="3">
         <v>2</v>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Broad: 'One flexible platform for every team and organization'; use-case tabs Sales, Onboarding, Managers, Tool rollouts, Healthcare, Partners; footer lists Revenue Teams, Sales Enablement, L&amp;D and others</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: No explicit pain on the homepage; skills gaps in high-stakes conversations; slow certification, manager coaching time and rep turnover implied by metric cards; Revenue Teams page: messaging drift across roles</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">AI that helps your team</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Trusted by 100s of teams including</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">One end-to-end platform for organization-wide enablement, powered by AI roleplays.</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get a Demo</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Try Yoodli Free</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Trusted by 100s of teams including
 Yoodli drives real impact across organizations and industries
 One system, powered by AI roleplays, that drives measurable outcomes</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The AI Platform for Human Skills</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified: no explicit differentiation claim found on the homepage</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://yoodli.ai/</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Redirect: https://www.yoodli.ai/ 301-redirected to https://yoodli.ai/ (1 redirect, HTTP 200). H1 verified as HTML &lt;h1&gt; (MUI Typography) with exact text "AI that helps your team"; it is followed by a CSS-animated rotating word list OUTSIDE the &lt;h1&gt; (spin_text keyframes) — "onboard faster", "certify partners", "win more deals", "communicate confidently", "adopt AI tools", "learn new concepts" — so the visible headline rotates (e.g. "AI that helps your team win more deals"); only the static &lt;h1&gt; text recorded. Eyebrow "The AI Platform for Human Skills" verified as &lt;p&gt; above the H1 (not an H2) and used as Positioning. H2 = first body H2 ("Trusted by 100s of teams including", logo-strip heading). Hero paragraph verified verbatim (&lt;br&gt;-split into two lines in HTML; joined with a space). CTAs verified as hero anchors: "Get a Demo" -&gt; https://yoodli.ai/talk-to-sales; "Try Yoodli Free" -&gt; https://app.yoodli.ai/signup (header nav duplicates "Try Yoodli"/"Get a Demo" excluded). Section headings verified as HTML &lt;h2&gt; in document order; hero tab buttons (Roleplays/Personas/Coach), integration-category &lt;h3&gt;s and use-case tab buttons excluded; no responsive duplicates found. Metric claims on page (e.g. "15,000+ employees certified at Google Cloud", "1,215 hrs of manager time saved each quarter at Snowflake") are vendor claims, not endorsed. ICP "every team and organization" from exact H2 "One flexible platform for every team and organization" (use-case tabs: Sales, Onboarding, Managers, Tool rollouts, Healthcare, Partners); page positions org-wide enablement rather than sales-only. Pain Point "Not verified" — no explicit pain-point statement found on homepage. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Pain Point: homepage has no explicit pain statement; the CRO page https://yoodli.ai/for-business/revenue-teams states a requirement, "As messaging evolves and products expand, execution across roles must stay aligned.", not a pain, so it was not used). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-9; Table C; Table E (Revenue Teams page)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: No 'only/first/unlike/#1/vs', comparison or 'why Yoodli' copy in the page body; homepage links no official comparison or 'why' page (the only 'why' links are external press articles). Excluded: 'TIME Best Inventions 2026' (award item in the Featured news list) and customer testimonials such as Loopio's 'most realistic interaction' (rendered as client-side animated word spans). Hero copy 'One end-to-end platform for organization-wide enablement, powered by AI roleplays.' is positioning, not a comparison. Capture: phase2/batches/batch11/captures/yoodli_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="90" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="43" ht="90" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Accent Technologies</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">accent-technologies.com</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sales Enablement &amp; Content Intelligence</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Deal Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
-      <c r="E48" s="3">
+      <c r="E43" s="3">
         <v>5</v>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: 'go-to-market teams' (body copy); role cards for Marketing, Sales, Customer Success, Sales Management, Sales Enablement and Data Operations; industry pages for regulated and industrial sellers</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ANALYST SUMMARY: Fragmented tools and information: 'not three versions of the truth'; reps hunting for content; 'Closing the data-to-deals gap.'; Sales Management page: stale numbers and forecasts that cannot be defended</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The AI-powered revenue enablement platform</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Every tool your team needs to sell. On one platform.</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Get the right AI-personalized content at the right time, guided coaching, and real visibility and recommendations into every deal so your team wins more, more often.</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEE A DEMO</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Not verified</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">What is revenue enablement?
 Closing the data-to-deals gap.
 What our customers say</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Accent is the AI-powered revenue enablement platform that helps go-to-market teams surface the right content, guide reps to the next best action, and turn insight into revenue.</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">'Built to replace ten tools, not add an eleventh.' ('Why Accent?' section H3) | 'Accent believes teams should work off the same information, not three versions of the truth.' ('What is revenue enablement?' section body)</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://accent-technologies.com/</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">No redirect (HTTP 200). H1 verified as HTML &lt;h1&gt; (styled as a bordered label/eyebrow); H2 verified as the hero &lt;h2&gt; immediately after it ("On one platform." is a colored &lt;span&gt; inside the same &lt;h2&gt;) — it is the only body &lt;h2&gt; on the page. Hero paragraph verified verbatim. Hero block contains no CTA anchor: Primary CTA "SEE A DEMO" verified as the persistent header button (-&gt; https://accent-technologies.com/accent-demo/; also repeated in footer "Like what you see so far?" block); Secondary CTA "Not verified" — no second hero/header CTA (header "DEMO" and nav "See a demo" -&gt; /demo are duplicates of the same action). Section headings verified as HTML &lt;h3&gt; in document order (selected by section structure since no further &lt;h2&gt;s exist). "What our customers say" — HTML is malformed (the heading text is followed by a second opening &lt;h3&gt; instead of &lt;/h3&gt;, so a naive parser swallows the testimonial carousel); visible heading text recorded only. Mega-menu header &lt;p&gt;s and footer &lt;h3&gt; excluded. Positioning exact from body &lt;p&gt; under "Closing the data-to-deals gap."; ICP "go-to-market teams" from that same sentence. Pain Point exact final sentence of the "What is revenue enablement?" paragraph. Other on-page text relevant to PitchSense: "enterprise-grade AI trained on your knowledge, not a public chatbot"; "Built to replace ten tools, not add an eleventh."; claim "teams save 25% of the time they used to spend locating and creating materials" (vendor claim, not endorsed). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: re-checked the homepage capture; the hero block has no CTA anchor and the header holds only the demo action, repeated as DEMO / SEE A DEMO / See a demo). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-10; Table C; Table E (homepage, Sales Management page)); the verbatim homepage values stay in the batch CSV.
 Positioning/Differentiation: Quote 1 is the &lt;h3&gt; directly under the 'Why Accent?' eyebrow; quote 2 is the last sentence of the &lt;p&gt; under H3 'What is revenue enablement?'; both in static HTML. Capture: phase2/batches/batch11/captures/accent_home.html. Homepage captured Oct 19, 2026.</t>
         </is>
       </c>
     </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granola</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">granola.ai</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conversation Intelligence / meeting automation</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Call Intelligence, Shared Memory</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 (+2 unverified)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: People in back-to-back meetings across functions (logo mix of tech and startup teams); a dedicated sales page addresses reps and 'Sales Managers and CROs'; enterprise page targets IT and legal buyers</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Choosing between listening and note-taking, bots in the room, and post-meeting admin: 'Don’t choose between listening and taking good notes.'; sales page adds coaching on memory instead of evidence</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The AI notepad for back-to-back meetings</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effortless notes, enhanced instantly.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes, actions and memory. Without a meeting bot.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Download for free</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effortless notes, enhanced instantly.
+For the doers
+Granola helps you before, during and after your meetings.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The AI notepad for back-to-back meetings</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Humans in the room, not bots' (Features section H3 under H2 "Works everywhere you do, how you do") | 'Granola doesn’t join your meeting. Instead, it transcribes in the background while you stay present' (paragraph under that H3)</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.granola.ai/</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fetched 200, no redirect (www.granola.ai). Identity: operating and independent (Granola, Inc.; footer "© Granola, Inc."); no acquisition banner; Series C reported March 2026 (third-party press, not a primary source). H1 verified as HTML &lt;h1&gt;. Hero copy = the two &lt;p&gt; elements directly under the H1 ("Notes, actions and memory." / "Without a meeting bot."), joined with a space. H2 = first body &lt;h2&gt; ("Effortless notes, enhanced instantly."); it appears twice in the HTML (responsive duplicate, counted once). Primary CTA "Download for free" verified as the hero &lt;a&gt; (-&gt; https://notes.granola.ai/download); "Available for macOS, Windows, iOS, Android" is a &lt;span&gt; note, not a CTA. Secondary CTA "Not verified": the hero holds only one anchor; the header "Talk to sales" (-&gt; /contact/sales?source=nav) and the icon-only header download link are navigation, not hero CTAs. Section headings = &lt;h2&gt; in document order (Section Heading 1 repeats the H2 because it is the first body section); before/during/after tab H3s and the duplicated tab panels, the three-word split H2 "Perfect" / "meeting" / "memory", nav mega-menu and footer excluded. Positioning = the &lt;h1&gt; (no separate category statement in the body; the &lt;meta name="description"&gt; and &lt;title&gt; repeat it: "The AI notepad for back-to-back meetings. Notes, actions and memory. Without a meeting bot."). ICP "busy people" from the exact &lt;h2&gt; "Helping busy people through busy days" (testimonials section); the nav card says "The AI notepad for people in back-to-back meetings" (nav, not used). Pain Point exact from the &lt;p&gt; under H3 "Give your full attention". Testimonials (Linear, Andreessen Horowitz, Vercel, Menlo Ventures, Nat Friedman) and logos are vendor claims. Memory-relevant: H2 "Perfect meeting memory" (Granola Chat) and MCP section "Use your meeting notes anywhere". HTML only; rendered view not checked. Homepage researched October 20, 2026; Category from the batch 12 Phase 1 Table A row (new company, pending integration into the Master Report). Gap-fill Oct 20, 2026: no Not-verified fields could be filled (Secondary CTA: the hero block in granola_home.html holds one anchor only; the CRO page cannot supply a homepage CTA). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Table A Target Buyer; Table B sections 2, 5, 7; Table C; CRO page /use-cases/sales); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: Both quotes are in the homepage Features section, present in server HTML (&lt;h3&gt; and the &lt;p&gt; beneath it). The hero line "Without a meeting bot." makes the same contrast. Excluded: CRO-page FAQ "How is this different from Gong?" (answer in client-side JSON: "Gong captures everything, Granola is what they actually act on."; official sales page, not homepage). Footer links excluded. Fetched 200, no redirect. All quotes string-matched against phase2/batches/batch12/captures/granola_home.html (whitespace/entities normalised). Homepage researched Oct 20, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="90" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read AI</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">read.ai</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conversation Intelligence</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
+        </is>
+      </c>
+      <c r="E45" s="3">
+        <v>7</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Broad knowledge workers and teams ('leading companies, universities, and platforms worldwide'); sellers addressed on the HubSpot and Salesforce integration pages; enterprise workspaces for IT</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Meetings without outcomes and busywork: 'Every meeting should have outcomes.'; context scattered across tools; manual CRM updates and late deal-risk signals on the CRM pages</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meetings In, Decisions Out</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the invite to the follow-through</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every meeting should have outcomes. Read AI turns meetings into outcomes. Summaries with context from your email and calendar, and AI agents that recommend what happens next.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get Started for Free</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From the invite to the follow-through
+Works with your favorite tools
+Meet Ada, Your Digital Twin</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read AI turns meetings into outcomes.</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Read AI is independent and platform-agnostic—connecting across all your tools to deliver truly unified insights.' (paragraph under H2 "Works with your favorite tools") | 'One assistant for everything' (H5, first card in the "Why choose Read AI?" H2 section)</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.read.ai/</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fetched 200, no redirect (www.read.ai). Identity: operating and independent (Read AI, Inc., Seattle; About page names backers Madrona, Goodwater, Smash Capital; press page lists Feb 26, 2026 Ada launch coverage; no acquisition found). Announcement banner: "Read AI now available as Claude Connector, ChatGPT App, and MCP Server". H1 verified as HTML &lt;h1&gt; ("Meetings In," + &lt;br&gt; + &lt;span&gt; "Decisions Out", joined with a space); the span carries a typer class (animated, text present in HTML). Note: the page uses four more &lt;h1&gt; tags in body cards ("Walk in ready", "Capture what was said", "Meeting ends, actions start", "Built with privacy at its core"); they are not the hero. Hero copy verified verbatim from p.homepage-hero__description (last clause inside a highlight &lt;span&gt;). H2 = first body &lt;h2&gt;; the &lt;h4&gt; "Use Read AI wherever you work" (app-download strip) precedes it and is not an H2. Primary CTA "Get Started for Free" verified as hero &lt;a&gt; (-&gt; app.read.ai/analytics/signup?utm_content=home_trial); "5 free meetings / month", "No install required", "No credit card" are plain text. Secondary CTA "Not verified": the hero has no second action button; the next anchors are the app-download tiles (ChatGPT, Claude, MCP, Windows, MacOS, Android, iPhone, Chrome), recorded in Table D, and the nav buttons "Book a Demo" / "Try for free!" are navigation. Section headings = &lt;h2&gt; in document order (nav mega-menu, h1 body cards, h5 benefit cards, footer link lists excluded). Positioning = second sentence of the hero paragraph; the &lt;meta name="description"&gt; reads "Read AI, the fastest growing AI meeting notetaker in the world, works wherever you work..." (vendor claim, not used). ICP from the exact logo-strip text "Eliminating busywork for millions at leading companies, universities, and platforms worldwide" (no role or team is named on the homepage). Pain Point = first sentence of the hero paragraph. Testimonials (U.S. Chamber of Commerce, Particle41, Tiger Sisters, Fortune, Nitrogen PR) and badges "SOC 2 Type 2 Certified", "GDPR Compliant", "HIPAA Compliant" are vendor claims. Memory-relevant: "Your team's context from calendar, email, past meetings, and CRM"; "Everything shared becomes context your whole team can search". HTML only; rendered view not checked. Homepage researched October 20, 2026; Category from the batch 12 Phase 1 Table A row (new company, pending integration into the Master Report). Gap-fill Oct 20, 2026: no Not-verified fields could be filled (Secondary CTA: no second hero action in readai_home.html; app-download tiles are a separate strip). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Table A Target Buyer; Table B sections 2, 4, 7; Table C; Table E; CRO page /integrations/hubspot); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: Both quotes present in server HTML (&lt;p&gt; and &lt;h5&gt;). The meta description's "the fastest growing AI meeting notetaker in the world" is a vendor claim in a meta tag and not used. Footer and nav excluded. Fetched 200, no redirect. All quotes string-matched against phase2/batches/batch12/captures/readai_home.html (whitespace/entities normalised). Homepage researched Oct 20, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day AI</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">day.ai</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
+        </is>
+      </c>
+      <c r="E46" s="3">
+        <v>7</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Revenue and go-to-market teams building on AI agents ('Watch how a revenue team builds with Day AI'); homepage diagram serves Sales, Customer Success, Support, EPD and the CEO; RevOps and GTM engineers run the control plane</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: CRM records that lose context and agents that do not improve: 'A monolithic agent running frozen skills out of a repo doesn’t improve'; manual CRM updates and unaudited automation</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scale your company brain</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. CONTEXT GRAPH</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day AI provides the context graph and agent control plane to quickly and securely upgrade your go-to-market harness.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get Started</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copy onboarding prompt</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. CONTEXT GRAPH
+2. AGENT CONTROL PLANE
+Not verified</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day AI provides the context graph and agent control plane to quickly and securely upgrade your go-to-market harness.</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'A monolithic agent running frozen skills out of a repo doesn’t improve — it isn’t alive.' (paragraph under H2 "2. AGENT CONTROL PLANE") | 'One central context graph that you control. Vast improvements in speed, cost, accuracy, and governance.' (paragraph under H2 "1. CONTEXT GRAPH")</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://day.ai/</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fetched 200, no redirect (day.ai). Identity: operating and independent (© 2026 Day AI, Inc.; About page links Sequoia-led Series A coverage; founder letter "Life After CRM" at lifeaftercrm.com; no acquisition found). Announcement banner: "NEW Life After CRM read the manifesto -&gt;". H1 verified as HTML &lt;h1&gt; ("scale" is an accent &lt;span&gt; inside it, followed by " your company brain", lower case as in HTML); the rotating words "eval / build / deploy / secure / accelerate" are separate &lt;span&gt;s outside the &lt;h1&gt; and not recorded. Hero copy verified as the &lt;p&gt; under the H1. H2 = first body &lt;h2&gt; ("1. CONTEXT GRAPH"). Primary CTA "Get Started" verified as hero &lt;a&gt; (-&gt; /get-started; trailing "-&gt;" is an aria-hidden &lt;span&gt;). Secondary CTA "Copy onboarding prompt" verified as a hero &lt;button&gt; (aria-label identical; client-side copy action, no href; logos Claude/OpenAI/Cursor inside it); a second icon button aria-label "More ways to start" opens a menu (client-side, not recorded). "Want a free month?" is a &lt;span&gt;. Section headings: the static HTML holds only two &lt;h2&gt; ("1. CONTEXT GRAPH", "2. AGENT CONTROL PLANE"), so Section Heading 3 is "Not verified" (h3 tab panels "1.1 FASTER AND CHEAPER", "2.1 AGENTS SHAPED LIKE PEOPLE" and the time/tokens/cost metric H3s excluded as tab content; "# trusted by" / "# testimonials" are &lt;p&gt; labels). Further sections may render client-side; not checked. Positioning = the hero paragraph (same sentence; no other category statement in the body). ICP "Not verified": the body names no buyer; the &lt;meta name="description"&gt; says "Built for teams running go-to-market on Claude." (meta, not visible body text) and the hero diagram aria-label lists Sales, Customer Success, Support, EPD and the CEO. Pain Point exact from the &lt;p&gt; under H2 "2. AGENT CONTROL PLANE". Vendor claims: "and 400+ others" (logo strip), context-graph benchmark "2.1x faster", "1.9x fewer" tokens, "2.6x cheaper"; customer testimonials (Kaveh Sarhangpour, Matt Gargano, Kevin Zell, Jeremy Horowitz/Coco AI, Grant Fuellenbach/Go First). Memory-relevant: "Customer Memory is an LLM-optimized ontology..."; "Every agent, on every team, reads and writes the same multiplayer context graph." HTML only; rendered view not checked. Homepage researched October 20, 2026; Category from the batch 12 Phase 1 Table A row (new company, pending integration into the Master Report). Gap-fill Oct 20, 2026: ICP filled from the CRO-relevant page https://day.ai/use-cases (&lt;h1&gt; "Watch how a revenue team builds with Day AI"); Section Heading 3 still Not verified (only two &lt;h2&gt; in the homepage HTML). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Table A Target Buyer; Table B sections 2, 5, 6; Table C; Table E; CRO page /use-cases); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: Both quotes are &lt;p&gt; text in server HTML. The context-graph benchmark ("2.1x faster", "2.6x cheaper" "without context graph" vs "with context graph") and testimonial "Day’s output was the only one that was actually usable" are vendor/customer claims and not used as the vendor's own differentiation statement. Banner "Life After CRM" (manifesto at lifeaftercrm.com) frames Day AI against CRM but is a link label. Fetched 200, no redirect. All quotes string-matched against phase2/batches/batch12/captures/dayai_home.html (whitespace/entities normalised). Homepage researched Oct 20, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oliv.ai</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliv.ai</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Call Intelligence, Deal Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
+        </is>
+      </c>
+      <c r="E47" s="3">
+        <v>8</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Revenue teams ('Agent OS for Revenue Teams'); team tabs for Sales Development, Sales, Sales Engineering, Onboarding, Customer Success, Account Expansion, Revenue Operations and Enablement; revenue leaders addressed on AI adoption</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Scattered context and costly point tools: 'Context Scattered across apps'; 'Budget locked in SaaS'; teams stuck at early AI adoption; Forecast page: forecasts without reasons and pipeline siloed across tools</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your Revenue Org, Powered by Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents for entire revenue lifecycle</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proactive AI agents that work with your team to prospect, close, retain, and expand your revenue.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Try in Sandbox</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Book a 7m Chat</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agents for entire revenue lifecycle
+Leaders want AI-native growth.
+Budget locked in SaaS</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agent OS for Revenue Teams</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'Every app your revenue team already runs on, now AI-native. At 70% less. That saving funds your agents.' (&lt;p&gt; under H2 "Same Apps at 70% Less") | 'Legacy tools spent a decade and $100M+ building these apps. AI lets us build them for a fraction, and we pass the saving on.' (&lt;p&gt; answer under "How is Oliv this reasonable?", same section)</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oliv.ai/</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fetched https://www.oliv.ai/ with curl (HTTP 200, no redirect). Announcement banner and header link "Extorted by Gong? Get Oliv CI free until your contract ends, plus free data migration!" -&gt; /gong-alternative (switch offer, not an ownership notice). H1 verified as HTML &lt;h1&gt; made of two &lt;span&gt;s with a &lt;br&gt; ("Your Revenue Org," / "Powered by Autonomous Agents"); recorded with a space. Eyebrow "Agent OS for Revenue Teams" is a &lt;span&gt; directly above the &lt;h1&gt; (not a heading) and is used as Positioning; footer tagline reads "The Agentic OS for Revenue Teams". H2 = first body &lt;h2&gt; ("Agents for entire revenue lifecycle", team-tab section). Hero paragraph verified as &lt;p&gt;. CTAs verified as hero anchors in document order: "Try in Sandbox" -&gt; https://sandbox.oliv.ai/ (target _blank), then "Book a 7m Chat" -&gt; /book-a-demo (data-track="booking_cta"; the same anchor appears twice in the hero block as a responsive duplicate, and again in the header nav). Primary/secondary assigned by document order; visual prominence not checked. Section headings are &lt;h2&gt;s in document order; the page renders most sections twice (mobile and desktop variants, e.g. "Budget locked in SaaS", "Same Apps at 70% Less", "Context Scattered across apps" / "Context scattered across apps"); duplicates excluded. Agent cards (Researcher, Prospector, Deal Driver, Coach and others) are &lt;p&gt;s inside team tab buttons, excluded. ICP "Revenue Teams" from the hero eyebrow; team tabs name Sales Development, Sales, Sales Engineering, Onboarding, Customer Success, Account Expansion, Revenue Operations and Enablement. Pain Point is the &lt;p&gt; under H2 "Context Scattered across apps". Vendor claims recorded as claims only: "Same Apps at 70% Less"; "Legacy tools spent a decade and $100M+ building these apps"; "100+ Oliv SLMs". Comparison sections name Gong, Clari, Salesloft, Gainsight, Highspot and Claude. Homepage researched October 20, 2026; Category from the new Phase 1 Table A row for this company (scope swap, not yet in the Master Report). Gap-fill Oct 20, 2026: no Not-verified fields to fill (all 11 fields verified from the homepage capture). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2, 4-10; Table C; Table E (homepage, CRO page /oliv-forecast)); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: Both quotes are &lt;p&gt;s in the "Same Apps at 70% Less" &lt;h2&gt; section (rendered twice as mobile and desktop variants; the desktop variant asks "How is Oliv so reasonable?"). The second is a vendor cost claim, recorded verbatim. Not used: banner "Extorted by Gong? Get Oliv CI free until your contract ends" (switch offer, not a differentiation statement) and the "Claude runs on your desktop and waits for your next prompt" comparison section (contrast with general assistants; a candidate third quote). Footer links official comparison pages /gong-alternative and /gainsight-alternative (not inspected). Fetched 200, no redirect. Quotes string-matched against phase2/batches/batch13/captures/oliv_home.html (whitespace/entities normalised). Homepage captured Oct 20, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glean</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glean.com</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Sales Agents &amp; Shared Memory</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Content Intelligence, Shared Memory</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 (+1 unverified)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: Large enterprises across every department: 'The world's leading enterprises'; industry tabs (financial services, healthcare, retail, engineering, professional services); Sales page targets AEs, SEs, managers and partners</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANALYST SUMMARY: AI cost growing faster than adoption: 'AI costs are accelerating faster.'; security and permission risk; Sales page: admin work, slow rep ramp and deal context chased across tools</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete context that makes AI work at enterprise scale.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The world's leading enterprises put AI to work with Glean.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified: the hero block holds only an eyebrow &lt;p&gt;, the &lt;h1&gt; and one CTA; no supporting paragraph in HTML</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a demo</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not verified: the hero has one CTA; the header pairs "Get a demo" with "Sign in" (login, not a conversion CTA)</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The world's leading enterprises put AI to work with Glean.
+AI adoption is accelerating. AI costs are accelerating faster. Glean is built for enterprise scale.
+Glean turns company knowledge into action without runaway model spend.</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enterprise AI that understands your company</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'AI adoption is accelerating. AI costs are accelerating faster. Glean is built for enterprise scale.' (problem-statement H2) | 'Glean turns company knowledge into action without runaway model spend.' (solution-section H2)</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.glean.com/</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company homepage analysed, as dispatched (Glean is a horizontal enterprise AI platform, not a sales product; its Sales department page /solutions/departments/sales is linked from the Solutions menu and is used as the CRO page in the full-format tables). Fetched https://www.glean.com/ with curl (HTTP 200, no redirect). Footer: "Glean Technologies, Inc."; header banner "See what's new" -&gt; /product-drop/october-2026. H1 verified as HTML &lt;h1&gt;. Eyebrow "Enterprise AI that understands your company" is a &lt;p&gt; above the &lt;h1&gt; and is used as Positioning. H2 = first body &lt;h2&gt; (logo-strip heading). Only one hero anchor ("Get a demo" -&gt; /get-a-demo, data-event home_hero_get_a_demo_click). Section headings are &lt;h2&gt;s in document order; the "Elevate your AI expertise" Glean:GO promo between the logos and the problem statement has no heading tag (only &lt;p&gt;s), so it is skipped. The problem-statement &lt;h2&gt; holds three sentences; recorded whole. The mega-menu (repeated three times for responsive layouts) and the footer heading duplicate "See Enterprise AI in action" are excluded. ICP "The world's leading enterprises" from the logo-strip &lt;h2&gt;; the customers section adds "One platform. Every team." and industry tabs (financial services, healthcare, retail, engineering, manufacturing, professional services). Pain Point is the first two sentences of the problem-statement &lt;h2&gt; (section id "problem-statement"). Vendor claims recorded as claims only: "40+ Unique LLMs", "110 hours Saved per user/year", "93% Enterprise adoption in &lt; 2 years", "275+" connectors, "3+ billion Searches", "99.9%+ Uptime", "Average token savings YTD: 12,442,032,540", Gartner "Market Shaper" report. Homepage researched October 20, 2026; Category from the new Phase 1 Table A row for this company (scope swap, not yet in the Master Report). Gap-fill Oct 20, 2026: no Not-verified fields could be filled (Hero Description: the hero has no supporting paragraph; Secondary CTA: the hero has a single CTA). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-10; Table C; Table E (homepage, CRO page /solutions/departments/sales)); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: No "only/first/unlike/vs" copy in the page body; the two quotes are the homepage &lt;h2&gt;s that set Glean apart on cost at enterprise scale (section ids "problem-statement" and "solution"). Footer links official comparison pages (Glean vs ChatGPT Enterprise, vs Microsoft 365 Copilot, vs Claude Enterprise; not inspected). Not used: statistics such as "93% Enterprise adoption in &lt; 2 years" (vendor metrics, not a differentiation statement) and the Gartner "Market Shaper" report title. Fetched 200, no redirect. Quotes string-matched against phase2/batches/batch13/captures/glean_home.html. Homepage captured Oct 20, 2026.</t>
+        </is>
+      </c>
+    </row>
     <row r="49" ht="90" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consensus</t>
+          <t xml:space="preserve">Spekit</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">goconsensus.com</t>
+          <t xml:space="preserve">spekit.com</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Enablement &amp; Content Intelligence (demo automation)</t>
+          <t xml:space="preserve">Sales Enablement &amp; Content Intelligence</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deal Intelligence, Content Intelligence, Shared Memory</t>
+          <t xml:space="preserve">Deal Intelligence, Content Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
       <c r="E49" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: B2B software revenue teams ('revenue teams like yours'); Solutions menu lists Presales, Sales, Channel, Marketing, Customer success</t>
+          <t xml:space="preserve">ANALYST SUMMARY: 'high-growth B2B revenue teams with high change velocity'; sales leaders, enablement, RevOps, product marketing and reps; dedicated CRO, Sales Leaders and Enablement pages</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Buying happens without the seller: 'Deals move without a rep in the room.'; buyers want to self-serve demos; hidden stakeholders ('No more mystery buyers')</t>
+          <t xml:space="preserve">ANALYST SUMMARY: Stale knowledge as the business changes: 'Products ship daily. Pricing moves. Messaging shifts mid-quarter.'; slow ramp; enablement stuck in portals; CRO page: stale answers that cost deals</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unleash your demo, unlock revenue.</t>
+          <t xml:space="preserve">AI-first revenue enablement for every rep and every agent</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every way your buyers want to see your product</t>
+          <t xml:space="preserve">For Revenue Teams Moving at 10x</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One demo platform for every way your buyers want to see your product, and every way your teams want to show it - agentic, self-guided, and live.</t>
+          <t xml:space="preserve">Reimagine revenue enablement with the AI-powered Rep Acceleration Platform. One governed source for content management, learning, coaching, content creation, digital sales rooms and deal intelligence delivered as Enablement in the Flow of Work®.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book a meeting</t>
+          <t xml:space="preserve">Book a Demo</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not verified</t>
+          <t xml:space="preserve">See Our Latest AI Deal Room Innovations</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every way your buyers want to see your product
-Customers see the impact
-One demo motion, from the first website visit to the live call</t>
+          <t xml:space="preserve">For Revenue Teams Moving at 10x
+Why teams choose Spekit
+Faster ramp, higher capacity, stronger wins.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">One demo platform for every way your buyers want to see your product, and every way your teams want to show it - agentic, self-guided, and live.</t>
+          <t xml:space="preserve">Spekit is an AI-native revenue enablement platform built for in-workflow execution.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'Consensus Live is the only solution in the space that lets us have our software do what it’s supposed to do and give us what we needed for demos.' (customer testimonial blockquote, 'Results from revenue teams like yours' section)</t>
+          <t xml:space="preserve">'Most enablement platforms still center on portals, file storage, and separate training systems. Spekit is built around execution: it governs knowledge, creates and updates content with AI, brings deal context into workflow, and helps reps act in the moment.' (FAQ answer to H3 "How is Spekit different from other enablement platforms?") | 'Yes. Spekit consolidates what most teams split across multiple tools: content management, governance, AI content creation, learning and onboarding, in-workflow coaching, Deal Rooms, and analytics.' (FAQ answer to H3 "Does Spekit replace Seismic, Highspot, or Mindtickle?")</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://goconsensus.com/</t>
+          <t xml:space="preserve">https://www.spekit.com/</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No redirect (HTTP 200). H1 verified as HTML &lt;h1 id="hero-title"&gt; ("your demo, unlock" is a styled &lt;span&gt; inside it); the &lt;h1&gt; carries a data-lp-replace attribute, so its text may be swapped client-side for some landing-page visitors — static HTML text recorded. H2 = first body H2 ("Every way your buyers want to see your product"). Hero paragraph verified verbatim (hyphen with spaces preserved as in HTML). Primary CTA "Book a meeting" verified as the only hero anchor (-&gt; https://goconsensus.com/talk-to-sales); Secondary CTA "Not verified" — hero contains a single CTA (header "Login" -&gt; app.goconsensus.com is a sign-in link, not a CTA; "Watch Video"/"Watch it in action" are later modal triggers #videoModal/#demoModal). Section headings verified as HTML &lt;h2&gt; in document order; eyebrow &lt;p&gt;s ("Platform", "Complete demo experience", "Demo intelligence", "Testimonials") and footer &lt;h3&gt;s excluded; no responsive duplicates. Positioning = the hero paragraph (no separate positioning statement). ICP "revenue teams like yours" from exact H2 "Results from revenue teams like yours"; related claim "More than half of the world’s top 30 software companies leverage Consensus to close deals 30% faster, double their win rates, and increase deal sizes by 1.5X." (vendor claim, not endorsed). Pain Point exact first sentence of the Demo Intelligence paragraph under H2 "Every interaction, one stream of intelligence.", which continues "...so you know who's involved, what they care about, and how to close when you do get the right people in a meeting." — buyer-committee/stakeholder intelligence messaging relevant to PitchSense. Footer links to comparison pages vs Walnut, Reprise, Navattic, Demostack, Storylane. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (Secondary CTA: re-checked the homepage capture; the hero btn-row holds a single anchor, "Book a meeting"; "Watch a 4-minute overview" is only in the closing CTA block). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-9; Table C; Table E (homepage, Sales solution page)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: Quote is a &lt;blockquote&gt; customer testimonial (Amelia Ochodnikcy, Distinguished, Strategic Solution Engineer) under H2 'Results from revenue teams like yours' — customer words displayed by the vendor, a vendor claim, not endorsed. No vendor-voiced 'only/unlike/vs' copy on the page; hero 'One demo platform for every way your buyers want to see your product...' is positioning, not a comparison. Capture: phase2/batches/batch11/captures/consensus_home.html. Homepage captured Oct 19, 2026.</t>
+          <t xml:space="preserve">Fetched https://www.spekit.com/ with curl (HTTP 200, no redirect). Announcement banner "Get Your SKO Deck" -&gt; https://theskodeck.com/. H1 verified as HTML &lt;h1&gt; ("for every rep" and "and every agent" are &lt;strong&gt;/&lt;em&gt; inside it). H2 = first body &lt;h2&gt;. Hero paragraph verified as &lt;p&gt;. CTAs verified as hero anchors: "Book a Demo" -&gt; /demo-request (default button variant); "See Our Latest AI Deal Room Innovations" -&gt; /reimagined-deal-rooms (text button variant). Header "Book a Demo" and "Login" excluded as nav. Section headings are &lt;h2&gt;s in document order; "Why teams choose Spekit" carries a trailing zero-width joiner in HTML (removed). Mega-menu &lt;h3&gt;s, FAQ &lt;h3&gt;s, testimonial &lt;h3&gt; quotes and the split "Your / Path / to 10X Revenue" animation &lt;h2&gt;s are excluded. Positioning is the first sentence of the FAQ answer to "What is Spekit?"; ICP from the FAQ answer to "Who is Spekit built for?" (which also names "sales leaders, enablement, RevOps, product marketing, and reps"). Pain Point: the only homepage pain statement ("Today’s opportunities are more complex than ever. Managers are stretched thinner than ever.") sits in a "block-cta" component placed after the &lt;footer&gt; whose visibility could not be confirmed in static HTML, so it was not used; Pain Point was left Not verified in the light capture and filled from the CRO page in gap-fill (see below). Vendor claims recorded as claims only: "3x ROI in under 12 months" (Q4), "25% Faster ramp time", "67% Faster onboarding", "Fastest ROI in the category.", Gartner Magic Quadrant recognition, G2 badges. Homepage researched October 20, 2026; Category from the new Phase 1 Table A row for this company (scope swap, not yet in the Master Report). Gap-fill Oct 20, 2026: Pain Point filled from the CRO page https://www.spekit.com/solutions/chief-revenue-officers, &lt;p&gt; under the H1 "Unlock more revenue per rep" ("Your product changed this week. Did your reps? Did your agents?" block). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2, 4-11; Table C; Table E (CRO page /solutions/chief-revenue-officers)); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: Both quotes are FAQ &lt;p&gt; answers under the H2 "Common Questions About Spekit". H2 "See what sets Spekit apart from the competition" links to the official /comparison page (not inspected). Not used: testimonial "Most enablement tools are big and bulky. Spekit is lighter, faster..." (customer quote, vendor-selected) and "Fastest ROI in the category." (vendor metric claim). Fetched 200, no redirect. Quotes string-matched against phase2/batches/batch13/captures/spekit_home.html. Homepage captured Oct 20, 2026.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="90" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reprise</t>
+          <t xml:space="preserve">Revenue Grid</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reprise.com</t>
+          <t xml:space="preserve">revenuegrid.com</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales Enablement &amp; Content Intelligence</t>
+          <t xml:space="preserve">Deal Intelligence &amp; RevOps</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content Intelligence</t>
+          <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence, Shared Memory</t>
         </is>
       </c>
       <c r="E50" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Not stated in the hero; persona sections for Solutions Engineering, Marketing and Sales; nav By team lists Presales, Sales, Marketing, Product marketing; enterprise software logos</t>
+          <t xml:space="preserve">ANALYST SUMMARY: Revenue teams in relationship-driven, compliance-heavy industries ('revenue teams operating where relationships, data, and compliance matter most'); Salesforce users; Sales Forecasting page addresses revenue leaders, sales and RevOps teams</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Not stated on the homepage; Sales page frames SE time consumed by live demos and unreliable demo environments ('No bugs, outages, or collisions from too many AEs')</t>
+          <t xml:space="preserve">ANALYST SUMMARY: Fragmented relationship data and manual CRM entry: 'turning fragmented data into a trusted source of truth'; missed moments to engage; Sales Forecasting page: forecasting as 'a guessing game' and revenue risk that surfaces too late</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The #1 Demo Platform</t>
+          <t xml:space="preserve">Transform Relationship Data into Revenue Growth</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An AI toolset that gives your agent demo superpowers</t>
+          <t xml:space="preserve">Trusted by 800K+ Revenue &amp; Operations Teams Worldwide</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The AI toolset your agent has been waiting for: data injection, product tours, full clones, and even video.</t>
+          <t xml:space="preserve">Empowering revenue teams to act proactively, engage with precision, and drive growth confidently, with a complete, trusted view of every client relationship.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get a Demo</t>
+          <t xml:space="preserve">Book a Demo</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Try for Free</t>
+          <t xml:space="preserve">Not verified: the hero has one CTA (&lt;button&gt; "Book a Demo"); the header pairs "Book a Demo" with "Login" (login, not a conversion CTA)</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">An AI toolset that gives your agent demo superpowers
-Demo creation via your preferred agent
-A Single Library for Your Entire Go-To-Market</t>
+          <t xml:space="preserve">Trusted by 800K+ Revenue &amp; Operations Teams Worldwide
+Revenue Grid automatically and securely captures every client interaction and syncs with your CRM – turning fragmented data into a trusted source of truth for every relationship.
+The Most Comprehensive and Secure Activity Capture Solution on the Market</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accelerate deals and increase win rates with the leading enterprise AI demo platform.</t>
+          <t xml:space="preserve">We’ve built Revenue Grid into the relationship intelligence platform for industries where trust is the operating currency.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'Accelerate deals and increase win rates with the leading enterprise AI demo platform.' (closing CTA section under H2 'Build Better Demos') | 'Reprise is the world’s leading AI demo platform.' (footer tagline)</t>
+          <t xml:space="preserve">'Only Revenue Grid applies smart, agentic intelligence to a complete and accurate relationship data that no other solution can replicate — making insights more accurate, recommendations more relevant, and actions more effective.' (&lt;p&gt; under H2 "Stronger Relationships through Intelligent Action") | 'The Most Comprehensive and Secure Activity Capture Solution on the Market' (H2, activity-capture section)</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.reprise.com/</t>
+          <t xml:space="preserve">https://revenuegrid.com/</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No redirect (HTTP 200). H1 verified as HTML &lt;h1&gt;; hero description is a &lt;div&gt; directly after the H1, verified verbatim. H2 = first body H2 — HTML is "An AI toolset&lt;br/&gt;that gives your agent demo superpowers"; &lt;br&gt; rendered as a space. CTAs verified as hero anchors: "Get a Demo" -&gt; /demo (data-wf button-primary), "Try for Free" -&gt; /free (button-secondary). Section headings verified as HTML &lt;h2&gt; in document order; EXCLUDED: four quoted prompt-style &lt;h2&gt;s (""Make that chart look better"", ""Populate this table with anonymized data"", ""Capture 20 screens of my app for a product tour"", ""Add a tour guide to my demo"") which are feature cards for MCP/Reveal/Replay/Replicate, and a customer-quote &lt;h2&gt; (Databricks testimonial) — not independent section headings; &lt;h3&gt; step cards (Get the data right, Demo live, etc.) also excluded. "Demo creation via your preferred agent" section links to a Claude directory listing (https://claude.ai/directory/reprise) and describes the Reprise MCP using "customer data like call transcripts and internal notes to personalize show stopping demos". Positioning exact from closing CTA block under H2 "Build Better Demos". ICP from exact persona H2s under "A Single Library for Your Entire Go-To-Market" (Solutions Engineering, Marketing, Sales). Pain Point "Not verified" — no explicit pain-point statement found on homepage. "#1" and "leading" are vendor claims, not endorsed. Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: Pain Point filled from the CRO page https://www.reprise.com/solutions/sales-leaders, &lt;p&gt; under H3 "An Environment You Can Trust" (Features section), exact text "No bugs, outages, or collisions from too many AEs in a sales demo environment." ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-8; Table C; Table E (homepage, Sales page)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: Quote 1 is the &lt;p&gt; under H2 'Build Better Demos' (closing CTA); quote 2 is the footer tagline &lt;p&gt; (markup splits it with HTML comments: 'world&lt;!-- --&gt;’&lt;!-- --&gt;s'; matches after removing comments; same text is in the page's JSON-LD description). Not used: Databricks case-study bullet 'Demos offer alternative to lengthy POC processes'. Capture: phase2/batches/batch11/captures/reprise_home.html. Homepage captured Oct 19, 2026.</t>
+          <t xml:space="preserve">Fetched https://revenuegrid.com/ with curl (HTTP 200, no redirect). No ownership, rebrand or acquisition banner; footer "© revenuegrid.com, 2026"; nav links Newsroom and "Funding Raised" ($20M Series A post). H1 verified as HTML &lt;h1&gt; made of two &lt;span class="h1-line"&gt; elements with no whitespace between them ("Transform Relationship" / "Data into Revenue Growth"; "Relationship" and "Revenue Growth" in &lt;em&gt;); recorded with a space. Hero &lt;p&gt; verified (three &lt;br&gt; line breaks, recorded as spaces). The hero holds one CTA: &lt;button class="hero-section__cta"&gt; "Book a Demo" with onclick to /request-demo/ (no href); Secondary CTA Not verified. Header has "Login" and "Book a Demo" anchors (desktop and responsive duplicates). H2 = first body &lt;h2&gt; ("Trusted by 800K+ Revenue &amp; Operations Teams Worldwide", partner/badge strip; "800K+" in &lt;span&gt;&lt;em&gt;, &lt;br&gt;s recorded as spaces). Section headings are body &lt;h2&gt;s in document order; mega-menu, mobile-menu and footer link lists excluded. Positioning is the CEO quote &lt;p&gt; in the quote section (Eric Holmen, CEO, Revenue Grid), recorded without its opening curly quote; &lt;meta name="description"&gt; reads "Revenue Intelligence platform that automatically captures sales activities to help you identify and fix revenue leaks." (not used). ICP is the tail of the testimonials &lt;h2&gt; "Trusted by revenue teams operating where relationships, data, and compliance matter most"; hero also says "Empowering revenue teams". Pain Point is the &lt;p&gt; under H3 "More time building relationships" (Productivity &amp; Growth At Scale section). Vendor claims recorded as claims only: "800K+" teams; G2 badge images (AI Sales Assistant Leader and others, identified from file names); "Only Revenue Grid applies smart, agentic intelligence ... that no other solution can replicate". Footer links comparison pages vs Salesforce Inbox and Einstein Activity Capture. Homepage researched October 20, 2026; Category from the new Phase 1 Table A row for this company (scope swap, not yet in the Master Report). Gap-fill Oct 20, 2026: no Not-verified fields could be filled (the hero holds a single &lt;button&gt; CTA; the next CTA, "Book a Call", sits in the later platform-tabs section). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 2-9; Table C; Table E (homepage, CRO page /product/sales-forecasting/)); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: First quote is the intro &lt;p&gt; (three &lt;p&gt; lines joined) under H2 "Stronger Relationships through Intelligent Action"; second is the activity-capture section &lt;h2&gt; (with inline &lt;span&gt;s). Both are vendor claims, recorded verbatim. Not used: the "800K+" scale claim (vendor metric, not a differentiation statement). Nav links official page /product/revenue-grid-vs-the-competition/ and footer links comparison pages vs Salesforce Inbox and Einstein Activity Capture (not inspected). Fetched 200, no redirect. Quotes string-matched against phase2/batches/batch14/captures/revenuegrid_home.html (whitespace/entities normalised). Homepage captured Oct 20, 2026.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="90" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dropbox (DocSend)</t>
+          <t xml:space="preserve">Weflow</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docsend.com</t>
+          <t xml:space="preserve">weflow.ai</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content Intelligence (document tracking)</t>
+          <t xml:space="preserve">Deal Intelligence &amp; RevOps</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Content Intelligence</t>
-        </is>
-      </c>
-      <c r="E51" s="3">
-        <v>1</v>
+          <t xml:space="preserve">Call Intelligence, Deal Intelligence, Coaching Intelligence</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 (+2 unverified)</t>
+        </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Not stated on the inspected pages; testimonials point to deal-making senders (agency CEO, finance manager, startup CEO, VC partner) sharing proposals, board materials and fundraising documents</t>
+          <t xml:space="preserve">ANALYST SUMMARY: RevOps and CROs at fast-growing companies on Salesforce ('Trusted by RevOps &amp; CROs in 300+ fast-growing companies'); persona tabs for Revenue Operations, Executives, Sales and Customer Success; Executives page targets B2B SaaS executives</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANALYST SUMMARY: Loss of control and insight after sending: 'Control every aspect of your shared documents, even after you hit send.'; no visibility into prospect engagement; framed as an upgrade from email attachments</t>
+          <t xml:space="preserve">ANALYST SUMMARY: Poor Salesforce data breaking the revenue process: 'a single source of distrust'; manual data entry, poor deal and pipeline visibility, no predictability; Executives page: forecast accuracy, quota attainment and late deal risk</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Securely share files with real-time control and insights</t>
+          <t xml:space="preserve">“It's like Gong with better AI and 50% the price.“</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Share and track with Dropbox DocSend</t>
+          <t xml:space="preserve">Poor Salesforce data makes your revenue process fail</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enjoy complete control over your most sensitive files after hitting send and sharpen your business proposals with valuable insights.</t>
+          <t xml:space="preserve">Automate Salesforce data capture with AI. Get full visibility into deals, pipeline, forecasts, and team performance.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Try DocSend</t>
+          <t xml:space="preserve">Get started</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explore plans</t>
+          <t xml:space="preserve">Take a tour</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Share and track with Dropbox DocSend
-DocSend is the easiest to setup, has the best ROI
-What DocSend customers are saying</t>
+          <t xml:space="preserve">Poor Salesforce data makes your revenue process fail
+A modular Revenue AI Platform to consolidate your stack.
+What you can do with Weflow:</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upgrade from traditional email attachments to DocSend links for enhanced security and a more polished, professional presentation.</t>
+          <t xml:space="preserve">Weflow is the Revenue AI Orchestration Platform for RevOps teams to coordinate humans, agents, and Salesforce data across the GTM motion.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'DocSend is the easiest to setup, has the best ROI' (H2 above review link) | 'Upgrade from traditional email attachments to DocSend links for enhanced security and a more polished, professional presentation.' (body copy under H2 'Share and track with Dropbox DocSend')</t>
+          <t xml:space="preserve">'“It's like Gong with better AI and 50% the price.“' (hero &lt;h1&gt;) | 'Why HolidayCheck chose Weflow over Gong' (customer-story card &lt;h3&gt; under H2 "Don't just take our word for it.")</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.dropbox.com/docsend</t>
+          <t xml:space="preserve">https://www.weflow.ai/</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entity / access note: DocSend's own homepage https://www.docsend.com/ (and https://docsend.com/) returned HTTP 403 with a Cloudflare "Just a moment..." challenge page to curl (no redirect issued); WebFetch also returned HTTP 403 — docsend.com content Not verified (page unfetchable). Fallback: Dropbox's official DocSend product landing page https://www.dropbox.com/docsend (HTTP 200, no redirect, canonical https://www.dropbox.com/docsend, &lt;title&gt; "DocSend - Dropbox") captured instead and used for every field; messaging may differ from docsend.com. H1 verified as HTML &lt;h1&gt; under eyebrow &lt;p&gt; "Dropbox DocSend". H2 = first body H2. Hero paragraph verified verbatim. CTAs verified as hero anchors: "Try DocSend" -&gt; https://docsend.com/signup; "Explore plans" -&gt; https://www.docsend.com/pricing/ (Dropbox global nav "Get started"/"Sign up" excluded). Section headings verified as HTML &lt;h2&gt; in document order; Dropbox mega-menu &lt;h3&gt;s (Teams/Use cases/Industries, each duplicated) excluded; final &lt;h2&gt; "For all files worth tracking" (closing CTA) not used. Positioning exact from first body paragraph under "Share and track with Dropbox DocSend"; feature copy includes "Gain actionable insights that drive your deals forward and build lasting relationships." and "virtual data rooms, file indexing and, one-click NDAs". "easiest to setup, has the best ROI" is a vendor/review claim, not endorsed. ICP "Not verified" — no explicit audience statement on this page (testimonials reference proposals, board decks, fund managers and fundraising). Pain Point "Not verified" — no explicit pain-point statement ("traditional email attachments" is framed as an upgrade, not a stated pain). Homepage researched October 19, 2026; Category retained from Master Report. Gap-fill Oct 19, 2026: no Not-verified fields could be filled (ICP and Pain Point: the Dropbox product page still states neither; the CRO page used, https://www.dropbox.com/business/solutions/sales, is a Dropbox-wide sales page that lists DocSend only as one tool ("Send pitches and proposals with DocSend"), so it cannot supply DocSend's own ICP or pain point). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Table A Target Buyer; Table B sections 3-5; Table C; Table E (product page, Dropbox for sales page)); the verbatim homepage values stay in the batch CSV.
-Positioning/Differentiation: docsend.com returned HTTP 403 (Cloudflare challenge; docsend_home.html / docsend_home_retry.html are the challenge pages) so, as in the batch row, the official Dropbox product page https://www.dropbox.com/docsend (capture dropbox_docsend.html) was used. Quote 1 is an &lt;h2&gt; followed by the link 'Check out our reviews' (review-based vendor claim, not endorsed); quote 2 is the &lt;p&gt; directly under H2 'Share and track with Dropbox DocSend' (displacement of email attachments). Both in static HTML. Capture: phase2/batches/batch11/captures/dropbox_docsend.html. Homepage captured Oct 19, 2026.</t>
+          <t xml:space="preserve">Fetched https://weflow.ai/ with curl: 301 to https://www.weflow.ai/ (HTTP 200). Former domain getweflow.com also returns 301 to https://www.weflow.ai/ (domain move, name unchanged); the nav Login still points to https://app.getweflow.app/login. No ownership or acquisition banner. H1 verified as HTML &lt;h1&gt;; it is a quotation in curly quotes (“...“, both U+201C) with a &lt;br&gt; after "with", recorded with a space; no attribution in the hero. Eyebrow "Revenue AI Platform" is a &lt;div&gt; label above the &lt;h1&gt; (not a heading). Hero &lt;p&gt; verified. Primary CTA "Get started" is the value attribute of the hero email form's &lt;input type="submit"&gt; (placeholder "Your work email...", form data-redirect /free-trial; HubSpot form), so it appears in an attribute, not as a text node. Secondary CTA "Take a tour" verified as hero &lt;a&gt; -&gt; /start-tour (target _blank). Primary/secondary by document order; visual prominence not checked. H2 = first body &lt;h2&gt; ("Poor Salesforce data makes your revenue process fail", eyebrow "The Problem"). Section headings are &lt;h2&gt;s in document order; nav dropdown &lt;h4&gt;s and footer excluded. Positioning is the &lt;meta name="description"&gt; (identical og:description and twitter:description; &lt;title&gt; "Weflow | Revenue AI Orchestration Platform for RevOps"); the visible hero states only the eyebrow "Revenue AI Platform". ICP from the logo-wall heading &lt;div class="heading-style-h6"&gt; "Trusted by RevOps &amp; CROs in 300+ fast-growing companies"; persona tabs name Revenue Operations, Executives, Sales and Customer Success. Pain Point is the &lt;p&gt; text under H2 "Poor Salesforce data makes your revenue process fail". Vendor claims recorded as claims only: H1 Gong comparison; "300+ fast-growing companies"; metrics "96% of MEDDIC fields populated in Salesforce", "+24% win rate using AI deal insights", "-60% slipped deals using AI deal warnings", "93% forecast accuracy running by combining"; customer quotes. Case-study cards compare Weflow with Gong, Einstein Activity Capture and Cirrus Insight. Homepage researched October 20, 2026; Category from the new Phase 1 Table A row for this company (scope swap, not yet in the Master Report). Gap-fill Oct 20, 2026: no Not-verified fields to fill (all 11 fields verified from the homepage capture; Primary CTA and Positioning are attribute text, see above). ICP and Pain Point in the combined table are analyst summaries from analyst_fields.csv (Light row; Table A Target Buyer; Table B sections 3-8; Table C; Table E (homepage, CRO page /solutions/executives)); the verbatim homepage values stay in the batch CSV.
+Positioning/Differentiation: First quote is the hero &lt;h1&gt; (a quotation in curly quotes, &lt;br&gt; recorded as a space; no attribution shown); second is a customer-story card &lt;h3&gt;. Not used: "Why ADVISA dropped Einstein Activity Capture for Weflow" and "Why United Fintech chose Weflow over Einstein Activity Capture and Cirrus Insight" (further switch-story titles) and testimonial "None of the other tools gave us a solution like Weflow." (customer quote, vendor-selected). Footer links the official /compare page "Weflow vs Competitors" (not inspected). weflow.ai and getweflow.com 301 to https://www.weflow.ai/ (200). Quotes string-matched against phase2/batches/batch14/captures/weflow_home.html. Homepage captured Oct 20, 2026.</t>
         </is>
       </c>
     </row>
